--- a/examples/福耀玻璃_Beta04_完整分析.xlsx
+++ b/examples/福耀玻璃_Beta04_完整分析.xlsx
@@ -39,15 +39,27 @@
       <color rgb="FF0000FF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0E0E0"/>
+        <bgColor rgb="00E0E0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0E0F0"/>
+        <bgColor rgb="00D0E0F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -55,21 +67,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,3499 +490,3590 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>定价</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>定价</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>资产</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>63254182536</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>56630407495</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="4" t="n">
         <v>50767498791</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="4" t="n">
         <v>44784893954</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>38423625184</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="4" t="n">
         <v>38826279607</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J2" s="4" t="n">
         <v>34490438670</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>现金</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>20713712160</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>19838830944</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="4" t="n">
         <v>18165180172</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="4" t="n">
         <v>15447688808</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="4" t="n">
         <v>10411885641</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" s="4" t="n">
         <v>10001551003</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J3" s="4" t="n">
         <v>6800777265</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>投资</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>524177494</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>272592774</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="4" t="n">
         <v>327607056</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="4" t="n">
         <v>298144705</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="4" t="n">
         <v>264748905</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" s="4" t="n">
         <v>199805151</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J4" s="4" t="n">
         <v>205738050</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>运营资产</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>16094542311</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="4" t="n">
         <v>14147469320</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="4" t="n">
         <v>12235113740</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="4" t="n">
         <v>10129858419</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="4" t="n">
         <v>8668361952</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" s="4" t="n">
         <v>8471317618</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J5" s="4" t="n">
         <v>9033666442</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>应收</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>8969464994</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>7496008772</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="4" t="n">
         <v>5461966571</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="4" t="n">
         <v>4350121771</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="4" t="n">
         <v>3753925498</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="4" t="n">
         <v>3477440317</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J6" s="4" t="n">
         <v>4304107516</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>预付</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>305455256</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>316529520</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="4" t="n">
         <v>235934604</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="4" t="n">
         <v>238959820</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="4" t="n">
         <v>173525313</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" s="4" t="n">
         <v>222501827</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J7" s="4" t="n">
         <v>220126772</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>存货</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>5970614068</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>5143615319</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="4" t="n">
         <v>5403360356</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="4" t="n">
         <v>4327048485</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="4" t="n">
         <v>3280989599</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" s="4" t="n">
         <v>3280465303</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J8" s="4" t="n">
         <v>3241739977</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>长期资产</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>25921750571</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>22371514457</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="4" t="n">
         <v>20039597823</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="4" t="n">
         <v>18909202022</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="4" t="n">
         <v>19078628686</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" s="4" t="n">
         <v>20153605835</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="J9" s="4" t="n">
         <v>18450256913</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>负债</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>27568613358</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>25219085168</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="4" t="n">
         <v>21779200663</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="4" t="n">
         <v>18490789663</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" s="4" t="n">
         <v>16832717886</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" s="4" t="n">
         <v>17457198085</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="J10" s="4" t="n">
         <v>14300566064</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>预收</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <v>807312590</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="4" t="n">
         <v>979067305</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="4" t="n">
         <v>931585408</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" s="4" t="n">
         <v>863737090</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" s="4" t="n">
         <v>756282114</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" s="4" t="n">
         <v>695400166</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="J11" s="4" t="n">
         <v>594503112</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>应付</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>5803094989</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>5522986739</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="4" t="n">
         <v>4153709622</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="4" t="n">
         <v>3148222805</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="4" t="n">
         <v>2466005390</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" s="4" t="n">
         <v>2097319605</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="J12" s="4" t="n">
         <v>2465349981</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>有息负债</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>14995298574</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <v>14535923962</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="4" t="n">
         <v>13012009563</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="4" t="n">
         <v>11205647043</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" s="4" t="n">
         <v>10434585123</v>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" s="4" t="n">
         <v>11383469538</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="J13" s="4" t="n">
         <v>8403278932</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>权益</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="4" t="n">
         <v>35685569178</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <v>31411322327</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="4" t="n">
         <v>28988298128</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="4" t="n">
         <v>26294104291</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" s="4" t="n">
         <v>21590907298</v>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" s="4" t="n">
         <v>21369081522</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="J14" s="4" t="n">
         <v>20189872606</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>资本投入</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="4" t="n">
         <v>12310494456</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="4" t="n">
         <v>12310494456</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" s="4" t="n">
         <v>12310494456</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" s="4" t="n">
         <v>12310494456</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" s="4" t="n">
         <v>8731529967</v>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I15" s="4" t="n">
         <v>8731695689</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="J15" s="4" t="n">
         <v>8731695689</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>未分配利润</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="4" t="n">
         <v>18625997091</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="4" t="n">
         <v>15007163446</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F16" s="4" t="n">
         <v>12989794025</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="4" t="n">
         <v>11245487054</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H16" s="4" t="n">
         <v>10305548562</v>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="I16" s="4" t="n">
         <v>9828694828</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="J16" s="4" t="n">
         <v>9150322858</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>股息分红</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="4" t="n">
         <v>4697538357.6</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="4" t="n">
         <v>3392666591.6</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" s="4" t="n">
         <v>3262179415</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="4" t="n">
         <v>2609743532</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" s="4" t="n">
         <v>1957307649</v>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="I17" s="4" t="n">
         <v>1881463149</v>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="J17" s="4" t="n">
         <v>2884910162</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>现金结构</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="4" t="n">
         <v>20713712160</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="4" t="n">
         <v>19838830944</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="4" t="n">
         <v>18165180172</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="4" t="n">
         <v>15447688808</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="4" t="n">
         <v>10411885641</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I19" s="4" t="n">
         <v>10001551003</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="J19" s="4" t="n">
         <v>6800777265</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>利润留存</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="4" t="n">
         <v>18625997091</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="4" t="n">
         <v>15007163446</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="4" t="n">
         <v>12989794025</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="4" t="n">
         <v>11245487054</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" s="4" t="n">
         <v>10305548562</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" s="4" t="n">
         <v>9828694828</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="J20" s="4" t="n">
         <v>9150322858</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>股东、负债</t>
         </is>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="6">
         <f>D3-D16</f>
         <v/>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="6">
         <f>E3-E16</f>
         <v/>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="6">
         <f>F3-F16</f>
         <v/>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="6">
         <f>G3-G16</f>
         <v/>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="6">
         <f>H3-H16</f>
         <v/>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="6">
         <f>I3-I16</f>
         <v/>
       </c>
-      <c r="J21" s="5">
+      <c r="J21" s="6">
         <f>J3-J16</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>折旧摊销</t>
         </is>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="4" t="n">
         <v>2727498647</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="4" t="n">
         <v>2522443359</v>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="F23" s="4" t="n">
         <v>2345067457</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" s="4" t="n">
         <v>2251652666</v>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H23" s="4" t="n">
         <v>2242004968</v>
       </c>
-      <c r="I23" s="3" t="n">
+      <c r="I23" s="4" t="n">
         <v>2130158309</v>
       </c>
-      <c r="J23" s="3" t="n">
+      <c r="J23" s="4" t="n">
         <v>1687167602</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>资本开支</t>
         </is>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="4" t="n">
         <v>5480872166</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="4" t="n">
         <v>4474711099</v>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="F24" s="4" t="n">
         <v>3130253387</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" s="4" t="n">
         <v>2328511864</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="4" t="n">
         <v>1772542963</v>
       </c>
-      <c r="I24" s="3" t="n">
+      <c r="I24" s="4" t="n">
         <v>2779502262</v>
       </c>
-      <c r="J24" s="3" t="n">
+      <c r="J24" s="4" t="n">
         <v>3591741242</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>股本</t>
         </is>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="4" t="n">
         <v>2609743532</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="E26" s="4" t="n">
         <v>2609743532</v>
       </c>
-      <c r="F26" s="3" t="n">
+      <c r="F26" s="4" t="n">
         <v>2609743532</v>
       </c>
-      <c r="G26" s="3" t="n">
+      <c r="G26" s="4" t="n">
         <v>2609743532</v>
       </c>
-      <c r="H26" s="3" t="n">
+      <c r="H26" s="4" t="n">
         <v>2508617532</v>
       </c>
-      <c r="I26" s="3" t="n">
+      <c r="I26" s="4" t="n">
         <v>2508617532</v>
       </c>
-      <c r="J26" s="3" t="n">
+      <c r="J26" s="4" t="n">
         <v>2508617532</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>主营收入</t>
         </is>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="4" t="n">
         <v>38710428679</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="E28" s="4" t="n">
         <v>32650176898</v>
       </c>
-      <c r="F28" s="3" t="n">
+      <c r="F28" s="4" t="n">
         <v>27650978801</v>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="G28" s="4" t="n">
         <v>23261134069</v>
       </c>
-      <c r="H28" s="3" t="n">
+      <c r="H28" s="4" t="n">
         <v>19641289272</v>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="I28" s="4" t="n">
         <v>20765088255</v>
       </c>
-      <c r="J28" s="3" t="n">
+      <c r="J28" s="4" t="n">
         <v>19883838974</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>主营成本</t>
         </is>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="4" t="n">
         <v>24922427939</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="E29" s="4" t="n">
         <v>21310091980</v>
       </c>
-      <c r="F29" s="3" t="n">
+      <c r="F29" s="4" t="n">
         <v>18410110199</v>
       </c>
-      <c r="G29" s="3" t="n">
+      <c r="G29" s="4" t="n">
         <v>15039848812</v>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" s="4" t="n">
         <v>11944882127</v>
       </c>
-      <c r="I29" s="3" t="n">
+      <c r="I29" s="4" t="n">
         <v>13060926884</v>
       </c>
-      <c r="J29" s="3" t="n">
+      <c r="J29" s="4" t="n">
         <v>11488667084</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>费用</t>
         </is>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="4" t="n">
         <v>5746301975</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="E30" s="4" t="n">
         <v>5427862941</v>
       </c>
-      <c r="F30" s="3" t="n">
+      <c r="F30" s="4" t="n">
         <v>4742246146</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="4" t="n">
         <v>4092374443</v>
       </c>
-      <c r="H30" s="3" t="n">
+      <c r="H30" s="4" t="n">
         <v>4366570267</v>
       </c>
-      <c r="I30" s="3" t="n">
+      <c r="I30" s="4" t="n">
         <v>4480060059</v>
       </c>
-      <c r="J30" s="3" t="n">
+      <c r="J30" s="4" t="n">
         <v>4418465472</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>研发费用</t>
         </is>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="4" t="n">
         <v>1677751298</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E31" s="4" t="n">
         <v>1403030121</v>
       </c>
-      <c r="F31" s="3" t="n">
+      <c r="F31" s="4" t="n">
         <v>1248592812</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" s="4" t="n">
         <v>997203019</v>
       </c>
-      <c r="H31" s="3" t="n">
+      <c r="H31" s="4" t="n">
         <v>815579258</v>
       </c>
-      <c r="I31" s="3" t="n">
+      <c r="I31" s="4" t="n">
         <v>813129835</v>
       </c>
-      <c r="J31" s="3" t="n">
+      <c r="J31" s="4" t="n">
         <v>887721987</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>销售费用</t>
         </is>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="4" t="n">
         <v>1180260909</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="E32" s="4" t="n">
         <v>1538783486</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="4" t="n">
         <v>1350721298</v>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="G32" s="4" t="n">
         <v>1150992397</v>
       </c>
-      <c r="H32" s="3" t="n">
+      <c r="H32" s="4" t="n">
         <v>1474366072</v>
       </c>
-      <c r="I32" s="3" t="n">
+      <c r="I32" s="4" t="n">
         <v>1481567161</v>
       </c>
-      <c r="J32" s="3" t="n">
+      <c r="J32" s="4" t="n">
         <v>1467671276</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>管理费用</t>
         </is>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="4" t="n">
         <v>2888289768</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="4" t="n">
         <v>2486049334</v>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="F33" s="4" t="n">
         <v>2142932036</v>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="G33" s="4" t="n">
         <v>1944179027</v>
       </c>
-      <c r="H33" s="3" t="n">
+      <c r="H33" s="4" t="n">
         <v>2076624937</v>
       </c>
-      <c r="I33" s="3" t="n">
+      <c r="I33" s="4" t="n">
         <v>2185363063</v>
       </c>
-      <c r="J33" s="3" t="n">
+      <c r="J33" s="4" t="n">
         <v>2063072209</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>损耗</t>
         </is>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="4" t="n">
         <v>-98548679</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="4" t="n">
         <v>-220776671</v>
       </c>
-      <c r="F34" s="3" t="n">
+      <c r="F34" s="4" t="n">
         <v>-150481522</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="4" t="n">
         <v>-23928049</v>
       </c>
-      <c r="H34" s="3" t="n">
+      <c r="H34" s="4" t="n">
         <v>38157119</v>
       </c>
-      <c r="I34" s="3" t="n">
+      <c r="I34" s="4" t="n">
         <v>-20103858</v>
       </c>
-      <c r="J34" s="3" t="n">
+      <c r="J34" s="4" t="n">
         <v>-51746308</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>其他收益</t>
         </is>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="4" t="n">
         <v>400415185</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="4" t="n">
         <v>262917177</v>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="4" t="n">
         <v>215071387</v>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="G35" s="4" t="n">
         <v>242337506</v>
       </c>
-      <c r="H35" s="3" t="n">
+      <c r="H35" s="4" t="n">
         <v>352820556</v>
       </c>
-      <c r="I35" s="3" t="n">
+      <c r="I35" s="4" t="n">
         <v>181754102</v>
       </c>
-      <c r="J35" s="3" t="n">
+      <c r="J35" s="4" t="n">
         <v>146750220</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>现金收益</t>
         </is>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="4" t="n">
         <v>924966003</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="4" t="n">
         <v>602544066</v>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="F36" s="4" t="n">
         <v>231495735</v>
       </c>
-      <c r="G36" s="3" t="n">
+      <c r="G36" s="4" t="n">
         <v>195413923</v>
       </c>
-      <c r="H36" s="3" t="n">
+      <c r="H36" s="4" t="n">
         <v>348762592</v>
       </c>
-      <c r="I36" s="3" t="n">
+      <c r="I36" s="4" t="n">
         <v>336984661</v>
       </c>
-      <c r="J36" s="3" t="n">
+      <c r="J36" s="4" t="n">
         <v>335452093</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>股权收益</t>
         </is>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="4" t="n">
         <v>-15801862</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="E37" s="4" t="n">
         <v>4290148</v>
       </c>
-      <c r="F37" s="3" t="n">
+      <c r="F37" s="4" t="n">
         <v>20962737</v>
       </c>
-      <c r="G37" s="3" t="n">
+      <c r="G37" s="4" t="n">
         <v>26975045</v>
       </c>
-      <c r="H37" s="3" t="n">
+      <c r="H37" s="4" t="n">
         <v>11843754</v>
       </c>
-      <c r="I37" s="3" t="n">
+      <c r="I37" s="4" t="n">
         <v>-5932899</v>
       </c>
-      <c r="J37" s="3" t="n">
+      <c r="J37" s="4" t="n">
         <v>667776495</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>利息支出</t>
         </is>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="4" t="n">
         <v>288507082</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="E38" s="4" t="n">
         <v>288319603</v>
       </c>
-      <c r="F38" s="3" t="n">
+      <c r="F38" s="4" t="n">
         <v>288122259</v>
       </c>
-      <c r="G38" s="3" t="n">
+      <c r="G38" s="4" t="n">
         <v>318940791</v>
       </c>
-      <c r="H38" s="3" t="n">
+      <c r="H38" s="4" t="n">
         <v>354752403</v>
       </c>
-      <c r="I38" s="3" t="n">
+      <c r="I38" s="4" t="n">
         <v>432679520</v>
       </c>
-      <c r="J38" s="3" t="n">
+      <c r="J38" s="4" t="n">
         <v>376230473</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>财务费用</t>
         </is>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="4" t="n">
         <v>35964048</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E39" s="4" t="n">
         <v>-361719066</v>
       </c>
-      <c r="F39" s="3" t="n">
+      <c r="F39" s="4" t="n">
         <v>-1036725297</v>
       </c>
-      <c r="G39" s="3" t="n">
+      <c r="G39" s="4" t="n">
         <v>536834250</v>
       </c>
-      <c r="H39" s="3" t="n">
+      <c r="H39" s="4" t="n">
         <v>429822814</v>
       </c>
-      <c r="I39" s="3" t="n">
+      <c r="I39" s="4" t="n">
         <v>-127469129</v>
       </c>
-      <c r="J39" s="3" t="n">
+      <c r="J39" s="4" t="n">
         <v>-250823052</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>其他业务</t>
         </is>
       </c>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
-      <c r="J40" s="3" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="4" t="n">
         <v>541228588</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="E41" s="4" t="n">
         <v>510819743</v>
       </c>
-      <c r="F41" s="3" t="n">
+      <c r="F41" s="4" t="n">
         <v>447775365</v>
       </c>
-      <c r="G41" s="3" t="n">
+      <c r="G41" s="4" t="n">
         <v>341929292</v>
       </c>
-      <c r="H41" s="3" t="n">
+      <c r="H41" s="4" t="n">
         <v>265304196</v>
       </c>
-      <c r="I41" s="3" t="n">
+      <c r="I41" s="4" t="n">
         <v>338789268</v>
       </c>
-      <c r="J41" s="3" t="n">
+      <c r="J41" s="4" t="n">
         <v>341146746</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>成本</t>
         </is>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="4" t="n">
         <v>108449502</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="E42" s="4" t="n">
         <v>114234160</v>
       </c>
-      <c r="F42" s="3" t="n">
+      <c r="F42" s="4" t="n">
         <v>125334935</v>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" s="4" t="n">
         <v>89204424</v>
       </c>
-      <c r="H42" s="3" t="n">
+      <c r="H42" s="4" t="n">
         <v>97335416</v>
       </c>
-      <c r="I42" s="3" t="n">
+      <c r="I42" s="4" t="n">
         <v>136627509</v>
       </c>
-      <c r="J42" s="3" t="n">
+      <c r="J42" s="4" t="n">
         <v>114387863</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>营业外</t>
         </is>
       </c>
-      <c r="D43" s="3" t="n"/>
-      <c r="E43" s="3" t="n"/>
-      <c r="F43" s="3" t="n"/>
-      <c r="G43" s="3" t="n"/>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="n"/>
-      <c r="J43" s="3" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" s="4" t="n">
         <v>35905331</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="E44" s="4" t="n">
         <v>49843149</v>
       </c>
-      <c r="F44" s="3" t="n">
+      <c r="F44" s="4" t="n">
         <v>80855034</v>
       </c>
-      <c r="G44" s="3" t="n">
+      <c r="G44" s="4" t="n">
         <v>217974835</v>
       </c>
-      <c r="H44" s="3" t="n">
+      <c r="H44" s="4" t="n">
         <v>57628048</v>
       </c>
-      <c r="I44" s="3" t="n">
+      <c r="I44" s="4" t="n">
         <v>109494454</v>
       </c>
-      <c r="J44" s="3" t="n">
+      <c r="J44" s="4" t="n">
         <v>60687441</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>成本</t>
         </is>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D45" s="4" t="n">
         <v>120136061</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="E45" s="4" t="n">
         <v>125106357</v>
       </c>
-      <c r="F45" s="3" t="n">
+      <c r="F45" s="4" t="n">
         <v>163122132</v>
       </c>
-      <c r="G45" s="3" t="n">
+      <c r="G45" s="4" t="n">
         <v>161162665</v>
       </c>
-      <c r="H45" s="3" t="n">
+      <c r="H45" s="4" t="n">
         <v>214664627</v>
       </c>
-      <c r="I45" s="3" t="n">
+      <c r="I45" s="4" t="n">
         <v>294294341</v>
       </c>
-      <c r="J45" s="3" t="n">
+      <c r="J45" s="4" t="n">
         <v>71545321</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>所得税</t>
         </is>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="4" t="n">
         <v>1486781220</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="4" t="n">
         <v>1086913641</v>
       </c>
-      <c r="F46" s="3" t="n">
+      <c r="F46" s="4" t="n">
         <v>826310042</v>
       </c>
-      <c r="G46" s="3" t="n">
+      <c r="G46" s="4" t="n">
         <v>675861301</v>
       </c>
-      <c r="H46" s="3" t="n">
+      <c r="H46" s="4" t="n">
         <v>511144107</v>
       </c>
-      <c r="I46" s="3" t="n">
+      <c r="I46" s="4" t="n">
         <v>332955880</v>
       </c>
-      <c r="J46" s="3" t="n">
+      <c r="J46" s="4" t="n">
         <v>855187629</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>盈利结构</t>
         </is>
       </c>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="n"/>
-      <c r="F49" s="3" t="n"/>
-      <c r="G49" s="3" t="n"/>
-      <c r="H49" s="3" t="n"/>
-      <c r="I49" s="3" t="n"/>
-      <c r="J49" s="3" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n"/>
+      <c r="J49" s="4" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>主营收入</t>
         </is>
       </c>
-      <c r="D50" s="3" t="n">
-        <v>38710428679</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>32650176898</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>27650978801</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>23261134069</v>
-      </c>
-      <c r="H50" s="3" t="n">
-        <v>19641289272</v>
-      </c>
-      <c r="I50" s="3" t="n">
-        <v>20765088255</v>
-      </c>
-      <c r="J50" s="3" t="n">
-        <v>19883838974</v>
+      <c r="D50" s="6">
+        <f>D28</f>
+        <v/>
+      </c>
+      <c r="E50" s="6">
+        <f>E28</f>
+        <v/>
+      </c>
+      <c r="F50" s="6">
+        <f>F28</f>
+        <v/>
+      </c>
+      <c r="G50" s="6">
+        <f>G28</f>
+        <v/>
+      </c>
+      <c r="H50" s="6">
+        <f>H28</f>
+        <v/>
+      </c>
+      <c r="I50" s="6">
+        <f>I28</f>
+        <v/>
+      </c>
+      <c r="J50" s="6">
+        <f>J28</f>
+        <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>主营成本</t>
         </is>
       </c>
-      <c r="D51" s="3" t="n">
-        <v>24922427939</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>21310091980</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>18410110199</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>15039848812</v>
-      </c>
-      <c r="H51" s="3" t="n">
-        <v>11944882127</v>
-      </c>
-      <c r="I51" s="3" t="n">
-        <v>13060926884</v>
-      </c>
-      <c r="J51" s="3" t="n">
-        <v>11488667084</v>
+      <c r="D51" s="6">
+        <f>D29</f>
+        <v/>
+      </c>
+      <c r="E51" s="6">
+        <f>E29</f>
+        <v/>
+      </c>
+      <c r="F51" s="6">
+        <f>F29</f>
+        <v/>
+      </c>
+      <c r="G51" s="6">
+        <f>G29</f>
+        <v/>
+      </c>
+      <c r="H51" s="6">
+        <f>H29</f>
+        <v/>
+      </c>
+      <c r="I51" s="6">
+        <f>I29</f>
+        <v/>
+      </c>
+      <c r="J51" s="6">
+        <f>J29</f>
+        <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>费用</t>
         </is>
       </c>
-      <c r="D52" s="3" t="n">
-        <v>5746301975</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>5427862941</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>4742246146</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>4092374443</v>
-      </c>
-      <c r="H52" s="3" t="n">
-        <v>4366570267</v>
-      </c>
-      <c r="I52" s="3" t="n">
-        <v>4480060059</v>
-      </c>
-      <c r="J52" s="3" t="n">
-        <v>4418465472</v>
+      <c r="D52" s="6">
+        <f>D30</f>
+        <v/>
+      </c>
+      <c r="E52" s="6">
+        <f>E30</f>
+        <v/>
+      </c>
+      <c r="F52" s="6">
+        <f>F30</f>
+        <v/>
+      </c>
+      <c r="G52" s="6">
+        <f>G30</f>
+        <v/>
+      </c>
+      <c r="H52" s="6">
+        <f>H30</f>
+        <v/>
+      </c>
+      <c r="I52" s="6">
+        <f>I30</f>
+        <v/>
+      </c>
+      <c r="J52" s="6">
+        <f>J30</f>
+        <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>损耗</t>
         </is>
       </c>
-      <c r="D53" s="3" t="n">
-        <v>-98548679</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>-220776671</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>-150481522</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>-23928049</v>
-      </c>
-      <c r="H53" s="3" t="n">
-        <v>38157119</v>
-      </c>
-      <c r="I53" s="3" t="n">
-        <v>-20103858</v>
-      </c>
-      <c r="J53" s="3" t="n">
-        <v>-51746308</v>
+      <c r="D53" s="6">
+        <f>D34</f>
+        <v/>
+      </c>
+      <c r="E53" s="6">
+        <f>E34</f>
+        <v/>
+      </c>
+      <c r="F53" s="6">
+        <f>F34</f>
+        <v/>
+      </c>
+      <c r="G53" s="6">
+        <f>G34</f>
+        <v/>
+      </c>
+      <c r="H53" s="6">
+        <f>H34</f>
+        <v/>
+      </c>
+      <c r="I53" s="6">
+        <f>I34</f>
+        <v/>
+      </c>
+      <c r="J53" s="6">
+        <f>J34</f>
+        <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>其他收益</t>
         </is>
       </c>
-      <c r="D54" s="3" t="n">
-        <v>400415185</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>262917177</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>215071387</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>242337506</v>
-      </c>
-      <c r="H54" s="3" t="n">
-        <v>352820556</v>
-      </c>
-      <c r="I54" s="3" t="n">
-        <v>181754102</v>
-      </c>
-      <c r="J54" s="3" t="n">
-        <v>146750220</v>
+      <c r="D54" s="6">
+        <f>D35</f>
+        <v/>
+      </c>
+      <c r="E54" s="6">
+        <f>E35</f>
+        <v/>
+      </c>
+      <c r="F54" s="6">
+        <f>F35</f>
+        <v/>
+      </c>
+      <c r="G54" s="6">
+        <f>G35</f>
+        <v/>
+      </c>
+      <c r="H54" s="6">
+        <f>H35</f>
+        <v/>
+      </c>
+      <c r="I54" s="6">
+        <f>I35</f>
+        <v/>
+      </c>
+      <c r="J54" s="6">
+        <f>J35</f>
+        <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>现金收益</t>
         </is>
       </c>
-      <c r="D55" s="3" t="n">
-        <v>924966003</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>602544066</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>231495735</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>195413923</v>
-      </c>
-      <c r="H55" s="3" t="n">
-        <v>348762592</v>
-      </c>
-      <c r="I55" s="3" t="n">
-        <v>336984661</v>
-      </c>
-      <c r="J55" s="3" t="n">
-        <v>335452093</v>
+      <c r="D55" s="6">
+        <f>D36</f>
+        <v/>
+      </c>
+      <c r="E55" s="6">
+        <f>E36</f>
+        <v/>
+      </c>
+      <c r="F55" s="6">
+        <f>F36</f>
+        <v/>
+      </c>
+      <c r="G55" s="6">
+        <f>G36</f>
+        <v/>
+      </c>
+      <c r="H55" s="6">
+        <f>H36</f>
+        <v/>
+      </c>
+      <c r="I55" s="6">
+        <f>I36</f>
+        <v/>
+      </c>
+      <c r="J55" s="6">
+        <f>J36</f>
+        <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>利息支出</t>
         </is>
       </c>
-      <c r="D56" s="3" t="n">
-        <v>288507082</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>288319603</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>288122259</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>318940791</v>
-      </c>
-      <c r="H56" s="3" t="n">
-        <v>354752403</v>
-      </c>
-      <c r="I56" s="3" t="n">
-        <v>432679520</v>
-      </c>
-      <c r="J56" s="3" t="n">
-        <v>376230473</v>
+      <c r="D56" s="6">
+        <f>D38</f>
+        <v/>
+      </c>
+      <c r="E56" s="6">
+        <f>E38</f>
+        <v/>
+      </c>
+      <c r="F56" s="6">
+        <f>F38</f>
+        <v/>
+      </c>
+      <c r="G56" s="6">
+        <f>G38</f>
+        <v/>
+      </c>
+      <c r="H56" s="6">
+        <f>H38</f>
+        <v/>
+      </c>
+      <c r="I56" s="6">
+        <f>I38</f>
+        <v/>
+      </c>
+      <c r="J56" s="6">
+        <f>J38</f>
+        <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>财务费用</t>
         </is>
       </c>
-      <c r="D57" s="3" t="n">
-        <v>35964048</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>-361719066</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>-1036725297</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>536834250</v>
-      </c>
-      <c r="H57" s="3" t="n">
-        <v>429822814</v>
-      </c>
-      <c r="I57" s="3" t="n">
-        <v>-127469129</v>
-      </c>
-      <c r="J57" s="3" t="n">
-        <v>-250823052</v>
+      <c r="D57" s="6">
+        <f>D39</f>
+        <v/>
+      </c>
+      <c r="E57" s="6">
+        <f>E39</f>
+        <v/>
+      </c>
+      <c r="F57" s="6">
+        <f>F39</f>
+        <v/>
+      </c>
+      <c r="G57" s="6">
+        <f>G39</f>
+        <v/>
+      </c>
+      <c r="H57" s="6">
+        <f>H39</f>
+        <v/>
+      </c>
+      <c r="I57" s="6">
+        <f>I39</f>
+        <v/>
+      </c>
+      <c r="J57" s="6">
+        <f>J39</f>
+        <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>所得税</t>
         </is>
       </c>
-      <c r="D58" s="3" t="n">
-        <v>1486781220</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>1086913641</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>826310042</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>675861301</v>
-      </c>
-      <c r="H58" s="3" t="n">
-        <v>511144107</v>
-      </c>
-      <c r="I58" s="3" t="n">
-        <v>332955880</v>
-      </c>
-      <c r="J58" s="3" t="n">
-        <v>855187629</v>
+      <c r="D58" s="6">
+        <f>D46</f>
+        <v/>
+      </c>
+      <c r="E58" s="6">
+        <f>E46</f>
+        <v/>
+      </c>
+      <c r="F58" s="6">
+        <f>F46</f>
+        <v/>
+      </c>
+      <c r="G58" s="6">
+        <f>G46</f>
+        <v/>
+      </c>
+      <c r="H58" s="6">
+        <f>H46</f>
+        <v/>
+      </c>
+      <c r="I58" s="6">
+        <f>I46</f>
+        <v/>
+      </c>
+      <c r="J58" s="6">
+        <f>J46</f>
+        <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>业务利润</t>
         </is>
       </c>
-      <c r="D59" s="5">
+      <c r="D59" s="6">
         <f>D50-D51-D52+D53+D54+D55-D56-D57-D58</f>
         <v/>
       </c>
-      <c r="E59" s="5">
+      <c r="E59" s="6">
         <f>E50-E51-E52+E53+E54+E55-E56-E57-E58</f>
         <v/>
       </c>
-      <c r="F59" s="5">
+      <c r="F59" s="6">
         <f>F50-F51-F52+F53+F54+F55-F56-F57-F58</f>
         <v/>
       </c>
-      <c r="G59" s="5">
+      <c r="G59" s="6">
         <f>G50-G51-G52+G53+G54+G55-G56-G57-G58</f>
         <v/>
       </c>
-      <c r="H59" s="5">
+      <c r="H59" s="6">
         <f>H50-H51-H52+H53+H54+H55-H56-H57-H58</f>
         <v/>
       </c>
-      <c r="I59" s="5">
+      <c r="I59" s="6">
         <f>I50-I51-I52+I53+I54+I55-I56-I57-I58</f>
         <v/>
       </c>
-      <c r="J59" s="5">
+      <c r="J59" s="6">
         <f>J50-J51-J52+J53+J54+J55-J56-J57-J58</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>股权收益</t>
         </is>
       </c>
-      <c r="D60" s="3" t="n">
-        <v>-15801862</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>4290148</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>20962737</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>26975045</v>
-      </c>
-      <c r="H60" s="3" t="n">
-        <v>11843754</v>
-      </c>
-      <c r="I60" s="3" t="n">
-        <v>-5932899</v>
-      </c>
-      <c r="J60" s="3" t="n">
-        <v>667776495</v>
+      <c r="D60" s="6">
+        <f>D37</f>
+        <v/>
+      </c>
+      <c r="E60" s="6">
+        <f>E37</f>
+        <v/>
+      </c>
+      <c r="F60" s="6">
+        <f>F37</f>
+        <v/>
+      </c>
+      <c r="G60" s="6">
+        <f>G37</f>
+        <v/>
+      </c>
+      <c r="H60" s="6">
+        <f>H37</f>
+        <v/>
+      </c>
+      <c r="I60" s="6">
+        <f>I37</f>
+        <v/>
+      </c>
+      <c r="J60" s="6">
+        <f>J37</f>
+        <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>其他业务利润</t>
         </is>
       </c>
-      <c r="D61" s="5">
+      <c r="D61" s="6">
         <f>D41-D42</f>
         <v/>
       </c>
-      <c r="E61" s="5">
+      <c r="E61" s="6">
         <f>E41-E42</f>
         <v/>
       </c>
-      <c r="F61" s="5">
+      <c r="F61" s="6">
         <f>F41-F42</f>
         <v/>
       </c>
-      <c r="G61" s="5">
+      <c r="G61" s="6">
         <f>G41-G42</f>
         <v/>
       </c>
-      <c r="H61" s="5">
+      <c r="H61" s="6">
         <f>H41-H42</f>
         <v/>
       </c>
-      <c r="I61" s="5">
+      <c r="I61" s="6">
         <f>I41-I42</f>
         <v/>
       </c>
-      <c r="J61" s="5">
+      <c r="J61" s="6">
         <f>J41-J42</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>营业外利润</t>
         </is>
       </c>
-      <c r="D62" s="5">
+      <c r="D62" s="6">
         <f>D44-D45</f>
         <v/>
       </c>
-      <c r="E62" s="5">
+      <c r="E62" s="6">
         <f>E44-E45</f>
         <v/>
       </c>
-      <c r="F62" s="5">
+      <c r="F62" s="6">
         <f>F44-F45</f>
         <v/>
       </c>
-      <c r="G62" s="5">
+      <c r="G62" s="6">
         <f>G44-G45</f>
         <v/>
       </c>
-      <c r="H62" s="5">
+      <c r="H62" s="6">
         <f>H44-H45</f>
         <v/>
       </c>
-      <c r="I62" s="5">
+      <c r="I62" s="6">
         <f>I44-I45</f>
         <v/>
       </c>
-      <c r="J62" s="5">
+      <c r="J62" s="6">
         <f>J44-J45</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>净利润</t>
         </is>
       </c>
-      <c r="D63" s="5">
+      <c r="D63" s="6">
         <f>D59+D60+D61+D62</f>
         <v/>
       </c>
-      <c r="E63" s="5">
+      <c r="E63" s="6">
         <f>E59+E60+E61+E62</f>
         <v/>
       </c>
-      <c r="F63" s="5">
+      <c r="F63" s="6">
         <f>F59+F60+F61+F62</f>
         <v/>
       </c>
-      <c r="G63" s="5">
+      <c r="G63" s="6">
         <f>G59+G60+G61+G62</f>
         <v/>
       </c>
-      <c r="H63" s="5">
+      <c r="H63" s="6">
         <f>H59+H60+H61+H62</f>
         <v/>
       </c>
-      <c r="I63" s="5">
+      <c r="I63" s="6">
         <f>I59+I60+I61+I62</f>
         <v/>
       </c>
-      <c r="J63" s="5">
+      <c r="J63" s="6">
         <f>J59+J60+J61+J62</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>分红</t>
         </is>
       </c>
-      <c r="D64" s="3" t="n">
-        <v>4697538357.6</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>3392666591.6</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>3262179415</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>2609743532</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>1957307649</v>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>1881463149</v>
-      </c>
-      <c r="J64" s="3" t="n">
-        <v>2884910162</v>
+      <c r="D64" s="6">
+        <f>D17</f>
+        <v/>
+      </c>
+      <c r="E64" s="6">
+        <f>E17</f>
+        <v/>
+      </c>
+      <c r="F64" s="6">
+        <f>F17</f>
+        <v/>
+      </c>
+      <c r="G64" s="6">
+        <f>G17</f>
+        <v/>
+      </c>
+      <c r="H64" s="6">
+        <f>H17</f>
+        <v/>
+      </c>
+      <c r="I64" s="6">
+        <f>I17</f>
+        <v/>
+      </c>
+      <c r="J64" s="6">
+        <f>J17</f>
+        <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>利润留存</t>
         </is>
       </c>
-      <c r="D65" s="5">
+      <c r="D65" s="6">
         <f>D63-D64</f>
         <v/>
       </c>
-      <c r="E65" s="5">
+      <c r="E65" s="6">
         <f>E63-E64</f>
         <v/>
       </c>
-      <c r="F65" s="5">
+      <c r="F65" s="6">
         <f>F63-F64</f>
         <v/>
       </c>
-      <c r="G65" s="5">
+      <c r="G65" s="6">
         <f>G63-G64</f>
         <v/>
       </c>
-      <c r="H65" s="5">
+      <c r="H65" s="6">
         <f>H63-H64</f>
         <v/>
       </c>
-      <c r="I65" s="5">
+      <c r="I65" s="6">
         <f>I63-I64</f>
         <v/>
       </c>
-      <c r="J65" s="5">
+      <c r="J65" s="6">
         <f>J63-J64</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>折旧摊销</t>
         </is>
       </c>
-      <c r="D66" s="3" t="n">
-        <v>2727498647</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>2522443359</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>2345067457</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>2251652666</v>
-      </c>
-      <c r="H66" s="3" t="n">
-        <v>2242004968</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>2130158309</v>
-      </c>
-      <c r="J66" s="3" t="n">
-        <v>1687167602</v>
+      <c r="D66" s="6">
+        <f>D23</f>
+        <v/>
+      </c>
+      <c r="E66" s="6">
+        <f>E23</f>
+        <v/>
+      </c>
+      <c r="F66" s="6">
+        <f>F23</f>
+        <v/>
+      </c>
+      <c r="G66" s="6">
+        <f>G23</f>
+        <v/>
+      </c>
+      <c r="H66" s="6">
+        <f>H23</f>
+        <v/>
+      </c>
+      <c r="I66" s="6">
+        <f>I23</f>
+        <v/>
+      </c>
+      <c r="J66" s="6">
+        <f>J23</f>
+        <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>CAPEX</t>
         </is>
       </c>
-      <c r="D67" s="3" t="n">
-        <v>5480872166</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>4474711099</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>3130253387</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>2328511864</v>
-      </c>
-      <c r="H67" s="3" t="n">
-        <v>1772542963</v>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>2779502262</v>
-      </c>
-      <c r="J67" s="3" t="n">
-        <v>3591741242</v>
+      <c r="D67" s="6">
+        <f>D24</f>
+        <v/>
+      </c>
+      <c r="E67" s="6">
+        <f>E24</f>
+        <v/>
+      </c>
+      <c r="F67" s="6">
+        <f>F24</f>
+        <v/>
+      </c>
+      <c r="G67" s="6">
+        <f>G24</f>
+        <v/>
+      </c>
+      <c r="H67" s="6">
+        <f>H24</f>
+        <v/>
+      </c>
+      <c r="I67" s="6">
+        <f>I24</f>
+        <v/>
+      </c>
+      <c r="J67" s="6">
+        <f>J24</f>
+        <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>现金留存</t>
         </is>
       </c>
-      <c r="D68" s="5">
+      <c r="D68" s="6">
         <f>D65+D66-D67</f>
         <v/>
       </c>
-      <c r="E68" s="5">
+      <c r="E68" s="6">
         <f>E65+E66-E67</f>
         <v/>
       </c>
-      <c r="F68" s="5">
+      <c r="F68" s="6">
         <f>F65+F66-F67</f>
         <v/>
       </c>
-      <c r="G68" s="5">
+      <c r="G68" s="6">
         <f>G65+G66-G67</f>
         <v/>
       </c>
-      <c r="H68" s="5">
+      <c r="H68" s="6">
         <f>H65+H66-H67</f>
         <v/>
       </c>
-      <c r="I68" s="5">
+      <c r="I68" s="6">
         <f>I65+I66-I67</f>
         <v/>
       </c>
-      <c r="J68" s="5">
+      <c r="J68" s="6">
         <f>J65+J66-J67</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>业务现金</t>
         </is>
       </c>
-      <c r="D69" s="5">
+      <c r="D69" s="6">
         <f>D59+D66-D67</f>
         <v/>
       </c>
-      <c r="E69" s="5">
+      <c r="E69" s="6">
         <f>E59+E66-E67</f>
         <v/>
       </c>
-      <c r="F69" s="5">
+      <c r="F69" s="6">
         <f>F59+F66-F67</f>
         <v/>
       </c>
-      <c r="G69" s="5">
+      <c r="G69" s="6">
         <f>G59+G66-G67</f>
         <v/>
       </c>
-      <c r="H69" s="5">
+      <c r="H69" s="6">
         <f>H59+H66-H67</f>
         <v/>
       </c>
-      <c r="I69" s="5">
+      <c r="I69" s="6">
         <f>I59+I66-I67</f>
         <v/>
       </c>
-      <c r="J69" s="5">
+      <c r="J69" s="6">
         <f>J59+J66-J67</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>经营周转</t>
         </is>
       </c>
-      <c r="D71" s="3" t="n"/>
-      <c r="E71" s="3" t="n"/>
-      <c r="F71" s="3" t="n"/>
-      <c r="G71" s="3" t="n"/>
-      <c r="H71" s="3" t="n"/>
-      <c r="I71" s="3" t="n"/>
-      <c r="J71" s="3" t="n"/>
+      <c r="D71" s="4" t="n"/>
+      <c r="E71" s="4" t="n"/>
+      <c r="F71" s="4" t="n"/>
+      <c r="G71" s="4" t="n"/>
+      <c r="H71" s="4" t="n"/>
+      <c r="I71" s="4" t="n"/>
+      <c r="J71" s="4" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>毛利率</t>
         </is>
       </c>
-      <c r="D72" s="5">
+      <c r="D72" s="6">
         <f>(D28-D29)/D28</f>
         <v/>
       </c>
-      <c r="E72" s="5">
+      <c r="E72" s="6">
         <f>(E28-E29)/E28</f>
         <v/>
       </c>
-      <c r="F72" s="5">
+      <c r="F72" s="6">
         <f>(F28-F29)/F28</f>
         <v/>
       </c>
-      <c r="G72" s="5">
+      <c r="G72" s="6">
         <f>(G28-G29)/G28</f>
         <v/>
       </c>
-      <c r="H72" s="5">
+      <c r="H72" s="6">
         <f>(H28-H29)/H28</f>
         <v/>
       </c>
-      <c r="I72" s="5">
+      <c r="I72" s="6">
         <f>(I28-I29)/I28</f>
         <v/>
       </c>
-      <c r="J72" s="5">
+      <c r="J72" s="6">
         <f>(J28-J29)/J28</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D73" s="5">
+      <c r="D73" s="6">
         <f>D30/D28</f>
         <v/>
       </c>
-      <c r="E73" s="5">
+      <c r="E73" s="6">
         <f>E30/E28</f>
         <v/>
       </c>
-      <c r="F73" s="5">
+      <c r="F73" s="6">
         <f>F30/F28</f>
         <v/>
       </c>
-      <c r="G73" s="5">
+      <c r="G73" s="6">
         <f>G30/G28</f>
         <v/>
       </c>
-      <c r="H73" s="5">
+      <c r="H73" s="6">
         <f>H30/H28</f>
         <v/>
       </c>
-      <c r="I73" s="5">
+      <c r="I73" s="6">
         <f>I30/I28</f>
         <v/>
       </c>
-      <c r="J73" s="5">
+      <c r="J73" s="6">
         <f>J30/J28</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>研发费率</t>
         </is>
       </c>
-      <c r="D74" s="5">
+      <c r="D74" s="6">
         <f>D31/D28</f>
         <v/>
       </c>
-      <c r="E74" s="5">
+      <c r="E74" s="6">
         <f>E31/E28</f>
         <v/>
       </c>
-      <c r="F74" s="5">
+      <c r="F74" s="6">
         <f>F31/F28</f>
         <v/>
       </c>
-      <c r="G74" s="5">
+      <c r="G74" s="6">
         <f>G31/G28</f>
         <v/>
       </c>
-      <c r="H74" s="5">
+      <c r="H74" s="6">
         <f>H31/H28</f>
         <v/>
       </c>
-      <c r="I74" s="5">
+      <c r="I74" s="6">
         <f>I31/I28</f>
         <v/>
       </c>
-      <c r="J74" s="5">
+      <c r="J74" s="6">
         <f>J31/J28</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>销售费率</t>
         </is>
       </c>
-      <c r="D75" s="5">
+      <c r="D75" s="6">
         <f>D32/D28</f>
         <v/>
       </c>
-      <c r="E75" s="5">
+      <c r="E75" s="6">
         <f>E32/E28</f>
         <v/>
       </c>
-      <c r="F75" s="5">
+      <c r="F75" s="6">
         <f>F32/F28</f>
         <v/>
       </c>
-      <c r="G75" s="5">
+      <c r="G75" s="6">
         <f>G32/G28</f>
         <v/>
       </c>
-      <c r="H75" s="5">
+      <c r="H75" s="6">
         <f>H32/H28</f>
         <v/>
       </c>
-      <c r="I75" s="5">
+      <c r="I75" s="6">
         <f>I32/I28</f>
         <v/>
       </c>
-      <c r="J75" s="5">
+      <c r="J75" s="6">
         <f>J32/J28</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>管理费率</t>
         </is>
       </c>
-      <c r="D76" s="5">
+      <c r="D76" s="6">
         <f>D33/D28</f>
         <v/>
       </c>
-      <c r="E76" s="5">
+      <c r="E76" s="6">
         <f>E33/E28</f>
         <v/>
       </c>
-      <c r="F76" s="5">
+      <c r="F76" s="6">
         <f>F33/F28</f>
         <v/>
       </c>
-      <c r="G76" s="5">
+      <c r="G76" s="6">
         <f>G33/G28</f>
         <v/>
       </c>
-      <c r="H76" s="5">
+      <c r="H76" s="6">
         <f>H33/H28</f>
         <v/>
       </c>
-      <c r="I76" s="5">
+      <c r="I76" s="6">
         <f>I33/I28</f>
         <v/>
       </c>
-      <c r="J76" s="5">
+      <c r="J76" s="6">
         <f>J33/J28</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>净利率</t>
         </is>
       </c>
-      <c r="D77" s="5">
+      <c r="D77" s="6">
         <f>D59/D28</f>
         <v/>
       </c>
-      <c r="E77" s="5">
+      <c r="E77" s="6">
         <f>E59/E28</f>
         <v/>
       </c>
-      <c r="F77" s="5">
+      <c r="F77" s="6">
         <f>F59/F28</f>
         <v/>
       </c>
-      <c r="G77" s="5">
+      <c r="G77" s="6">
         <f>G59/G28</f>
         <v/>
       </c>
-      <c r="H77" s="5">
+      <c r="H77" s="6">
         <f>H59/H28</f>
         <v/>
       </c>
-      <c r="I77" s="5">
+      <c r="I77" s="6">
         <f>I59/I28</f>
         <v/>
       </c>
-      <c r="J77" s="5">
+      <c r="J77" s="6">
         <f>J59/J28</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>应收占比</t>
         </is>
       </c>
-      <c r="D79" s="5">
+      <c r="D79" s="6">
         <f>D6/D28</f>
         <v/>
       </c>
-      <c r="E79" s="5">
+      <c r="E79" s="6">
         <f>E6/E28</f>
         <v/>
       </c>
-      <c r="F79" s="5">
+      <c r="F79" s="6">
         <f>F6/F28</f>
         <v/>
       </c>
-      <c r="G79" s="5">
+      <c r="G79" s="6">
         <f>G6/G28</f>
         <v/>
       </c>
-      <c r="H79" s="5">
+      <c r="H79" s="6">
         <f>H6/H28</f>
         <v/>
       </c>
-      <c r="I79" s="5">
+      <c r="I79" s="6">
         <f>I6/I28</f>
         <v/>
       </c>
-      <c r="J79" s="5">
+      <c r="J79" s="6">
         <f>J6/J28</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>应收周转</t>
         </is>
       </c>
-      <c r="D80" s="5">
+      <c r="D80" s="6">
         <f>D28/D6</f>
         <v/>
       </c>
-      <c r="E80" s="5">
+      <c r="E80" s="6">
         <f>E28/E6</f>
         <v/>
       </c>
-      <c r="F80" s="5">
+      <c r="F80" s="6">
         <f>F28/F6</f>
         <v/>
       </c>
-      <c r="G80" s="5">
+      <c r="G80" s="6">
         <f>G28/G6</f>
         <v/>
       </c>
-      <c r="H80" s="5">
+      <c r="H80" s="6">
         <f>H28/H6</f>
         <v/>
       </c>
-      <c r="I80" s="5">
+      <c r="I80" s="6">
         <f>I28/I6</f>
         <v/>
       </c>
-      <c r="J80" s="5">
+      <c r="J80" s="6">
         <f>J28/J6</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>存货周转</t>
         </is>
       </c>
-      <c r="D81" s="5">
+      <c r="D81" s="6">
         <f>D29/D8</f>
         <v/>
       </c>
-      <c r="E81" s="5">
+      <c r="E81" s="6">
         <f>E29/E8</f>
         <v/>
       </c>
-      <c r="F81" s="5">
+      <c r="F81" s="6">
         <f>F29/F8</f>
         <v/>
       </c>
-      <c r="G81" s="5">
+      <c r="G81" s="6">
         <f>G29/G8</f>
         <v/>
       </c>
-      <c r="H81" s="5">
+      <c r="H81" s="6">
         <f>H29/H8</f>
         <v/>
       </c>
-      <c r="I81" s="5">
+      <c r="I81" s="6">
         <f>I29/I8</f>
         <v/>
       </c>
-      <c r="J81" s="5">
+      <c r="J81" s="6">
         <f>J29/J8</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>应付（预付）占比</t>
         </is>
       </c>
-      <c r="D82" s="5">
+      <c r="D82" s="6">
         <f>(D12+D7)/D28</f>
         <v/>
       </c>
-      <c r="E82" s="5">
+      <c r="E82" s="6">
         <f>(E12+E7)/E28</f>
         <v/>
       </c>
-      <c r="F82" s="5">
+      <c r="F82" s="6">
         <f>(F12+F7)/F28</f>
         <v/>
       </c>
-      <c r="G82" s="5">
+      <c r="G82" s="6">
         <f>(G12+G7)/G28</f>
         <v/>
       </c>
-      <c r="H82" s="5">
+      <c r="H82" s="6">
         <f>(H12+H7)/H28</f>
         <v/>
       </c>
-      <c r="I82" s="5">
+      <c r="I82" s="6">
         <f>(I12+I7)/I28</f>
         <v/>
       </c>
-      <c r="J82" s="5">
+      <c r="J82" s="6">
         <f>(J12+J7)/J28</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>预收占比</t>
         </is>
       </c>
-      <c r="D83" s="5">
+      <c r="D83" s="6">
         <f>D11/D28</f>
         <v/>
       </c>
-      <c r="E83" s="5">
+      <c r="E83" s="6">
         <f>E11/E28</f>
         <v/>
       </c>
-      <c r="F83" s="5">
+      <c r="F83" s="6">
         <f>F11/F28</f>
         <v/>
       </c>
-      <c r="G83" s="5">
+      <c r="G83" s="6">
         <f>G11/G28</f>
         <v/>
       </c>
-      <c r="H83" s="5">
+      <c r="H83" s="6">
         <f>H11/H28</f>
         <v/>
       </c>
-      <c r="I83" s="5">
+      <c r="I83" s="6">
         <f>I11/I28</f>
         <v/>
       </c>
-      <c r="J83" s="5">
+      <c r="J83" s="6">
         <f>J11/J28</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>利息支出/业务利润</t>
         </is>
       </c>
-      <c r="D84" s="5">
+      <c r="D84" s="6">
         <f>D38/D59</f>
         <v/>
       </c>
-      <c r="E84" s="5">
+      <c r="E84" s="6">
         <f>E38/E59</f>
         <v/>
       </c>
-      <c r="F84" s="5">
+      <c r="F84" s="6">
         <f>F38/F59</f>
         <v/>
       </c>
-      <c r="G84" s="5">
+      <c r="G84" s="6">
         <f>G38/G59</f>
         <v/>
       </c>
-      <c r="H84" s="5">
+      <c r="H84" s="6">
         <f>H38/H59</f>
         <v/>
       </c>
-      <c r="I84" s="5">
+      <c r="I84" s="6">
         <f>I38/I59</f>
         <v/>
       </c>
-      <c r="J84" s="5">
+      <c r="J84" s="6">
         <f>J38/J59</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>折旧摊销/长期资产</t>
         </is>
       </c>
-      <c r="D85" s="5">
+      <c r="D85" s="6">
         <f>D23/D9</f>
         <v/>
       </c>
-      <c r="E85" s="5">
+      <c r="E85" s="6">
         <f>E23/E9</f>
         <v/>
       </c>
-      <c r="F85" s="5">
+      <c r="F85" s="6">
         <f>F23/F9</f>
         <v/>
       </c>
-      <c r="G85" s="5">
+      <c r="G85" s="6">
         <f>G23/G9</f>
         <v/>
       </c>
-      <c r="H85" s="5">
+      <c r="H85" s="6">
         <f>H23/H9</f>
         <v/>
       </c>
-      <c r="I85" s="5">
+      <c r="I85" s="6">
         <f>I23/I9</f>
         <v/>
       </c>
-      <c r="J85" s="5">
+      <c r="J85" s="6">
         <f>J23/J9</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>资产结构</t>
         </is>
       </c>
-      <c r="D87" s="3" t="n"/>
-      <c r="E87" s="3" t="n"/>
-      <c r="F87" s="3" t="n"/>
-      <c r="G87" s="3" t="n"/>
-      <c r="H87" s="3" t="n"/>
-      <c r="I87" s="3" t="n"/>
-      <c r="J87" s="3" t="n"/>
+      <c r="D87" s="4" t="n"/>
+      <c r="E87" s="4" t="n"/>
+      <c r="F87" s="4" t="n"/>
+      <c r="G87" s="4" t="n"/>
+      <c r="H87" s="4" t="n"/>
+      <c r="I87" s="4" t="n"/>
+      <c r="J87" s="4" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>现金资产</t>
         </is>
       </c>
-      <c r="D88" s="5">
+      <c r="D88" s="6">
         <f>D3/D2</f>
         <v/>
       </c>
-      <c r="E88" s="5">
+      <c r="E88" s="6">
         <f>E3/E2</f>
         <v/>
       </c>
-      <c r="F88" s="5">
+      <c r="F88" s="6">
         <f>F3/F2</f>
         <v/>
       </c>
-      <c r="G88" s="5">
+      <c r="G88" s="6">
         <f>G3/G2</f>
         <v/>
       </c>
-      <c r="H88" s="5">
+      <c r="H88" s="6">
         <f>H3/H2</f>
         <v/>
       </c>
-      <c r="I88" s="5">
+      <c r="I88" s="6">
         <f>I3/I2</f>
         <v/>
       </c>
-      <c r="J88" s="5">
+      <c r="J88" s="6">
         <f>J3/J2</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>股权资产</t>
         </is>
       </c>
-      <c r="D89" s="5">
+      <c r="D89" s="6">
         <f>D4/D2</f>
         <v/>
       </c>
-      <c r="E89" s="5">
+      <c r="E89" s="6">
         <f>E4/E2</f>
         <v/>
       </c>
-      <c r="F89" s="5">
+      <c r="F89" s="6">
         <f>F4/F2</f>
         <v/>
       </c>
-      <c r="G89" s="5">
+      <c r="G89" s="6">
         <f>G4/G2</f>
         <v/>
       </c>
-      <c r="H89" s="5">
+      <c r="H89" s="6">
         <f>H4/H2</f>
         <v/>
       </c>
-      <c r="I89" s="5">
+      <c r="I89" s="6">
         <f>I4/I2</f>
         <v/>
       </c>
-      <c r="J89" s="5">
+      <c r="J89" s="6">
         <f>J4/J2</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>经营资产</t>
         </is>
       </c>
-      <c r="D90" s="5">
+      <c r="D90" s="6">
         <f>D5/D2</f>
         <v/>
       </c>
-      <c r="E90" s="5">
+      <c r="E90" s="6">
         <f>E5/E2</f>
         <v/>
       </c>
-      <c r="F90" s="5">
+      <c r="F90" s="6">
         <f>F5/F2</f>
         <v/>
       </c>
-      <c r="G90" s="5">
+      <c r="G90" s="6">
         <f>G5/G2</f>
         <v/>
       </c>
-      <c r="H90" s="5">
+      <c r="H90" s="6">
         <f>H5/H2</f>
         <v/>
       </c>
-      <c r="I90" s="5">
+      <c r="I90" s="6">
         <f>I5/I2</f>
         <v/>
       </c>
-      <c r="J90" s="5">
+      <c r="J90" s="6">
         <f>J5/J2</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>长期资产</t>
         </is>
       </c>
-      <c r="D91" s="5">
+      <c r="D91" s="6">
         <f>D9/D2</f>
         <v/>
       </c>
-      <c r="E91" s="5">
+      <c r="E91" s="6">
         <f>E9/E2</f>
         <v/>
       </c>
-      <c r="F91" s="5">
+      <c r="F91" s="6">
         <f>F9/F2</f>
         <v/>
       </c>
-      <c r="G91" s="5">
+      <c r="G91" s="6">
         <f>G9/G2</f>
         <v/>
       </c>
-      <c r="H91" s="5">
+      <c r="H91" s="6">
         <f>H9/H2</f>
         <v/>
       </c>
-      <c r="I91" s="5">
+      <c r="I91" s="6">
         <f>I9/I2</f>
         <v/>
       </c>
-      <c r="J91" s="5">
+      <c r="J91" s="6">
         <f>J9/J2</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>负债结构</t>
         </is>
       </c>
-      <c r="D92" s="3" t="n"/>
-      <c r="E92" s="3" t="n"/>
-      <c r="F92" s="3" t="n"/>
-      <c r="G92" s="3" t="n"/>
-      <c r="H92" s="3" t="n"/>
-      <c r="I92" s="3" t="n"/>
-      <c r="J92" s="3" t="n"/>
+      <c r="D92" s="4" t="n"/>
+      <c r="E92" s="4" t="n"/>
+      <c r="F92" s="4" t="n"/>
+      <c r="G92" s="4" t="n"/>
+      <c r="H92" s="4" t="n"/>
+      <c r="I92" s="4" t="n"/>
+      <c r="J92" s="4" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>经营负债</t>
         </is>
       </c>
-      <c r="D93" s="5">
+      <c r="D93" s="6">
         <f>(D11+D12)/D10</f>
         <v/>
       </c>
-      <c r="E93" s="5">
+      <c r="E93" s="6">
         <f>(E11+E12)/E10</f>
         <v/>
       </c>
-      <c r="F93" s="5">
+      <c r="F93" s="6">
         <f>(F11+F12)/F10</f>
         <v/>
       </c>
-      <c r="G93" s="5">
+      <c r="G93" s="6">
         <f>(G11+G12)/G10</f>
         <v/>
       </c>
-      <c r="H93" s="5">
+      <c r="H93" s="6">
         <f>(H11+H12)/H10</f>
         <v/>
       </c>
-      <c r="I93" s="5">
+      <c r="I93" s="6">
         <f>(I11+I12)/I10</f>
         <v/>
       </c>
-      <c r="J93" s="5">
+      <c r="J93" s="6">
         <f>(J11+J12)/J10</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>有息负债</t>
         </is>
       </c>
-      <c r="D94" s="5">
+      <c r="D94" s="6">
         <f>D13/D10</f>
         <v/>
       </c>
-      <c r="E94" s="5">
+      <c r="E94" s="6">
         <f>E13/E10</f>
         <v/>
       </c>
-      <c r="F94" s="5">
+      <c r="F94" s="6">
         <f>F13/F10</f>
         <v/>
       </c>
-      <c r="G94" s="5">
+      <c r="G94" s="6">
         <f>G13/G10</f>
         <v/>
       </c>
-      <c r="H94" s="5">
+      <c r="H94" s="6">
         <f>H13/H10</f>
         <v/>
       </c>
-      <c r="I94" s="5">
+      <c r="I94" s="6">
         <f>I13/I10</f>
         <v/>
       </c>
-      <c r="J94" s="5">
+      <c r="J94" s="6">
         <f>J13/J10</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>权益结构</t>
         </is>
       </c>
-      <c r="D95" s="3" t="n"/>
-      <c r="E95" s="3" t="n"/>
-      <c r="F95" s="3" t="n"/>
-      <c r="G95" s="3" t="n"/>
-      <c r="H95" s="3" t="n"/>
-      <c r="I95" s="3" t="n"/>
-      <c r="J95" s="3" t="n"/>
+      <c r="D95" s="4" t="n"/>
+      <c r="E95" s="4" t="n"/>
+      <c r="F95" s="4" t="n"/>
+      <c r="G95" s="4" t="n"/>
+      <c r="H95" s="4" t="n"/>
+      <c r="I95" s="4" t="n"/>
+      <c r="J95" s="4" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>资本投入</t>
         </is>
       </c>
-      <c r="D96" s="5">
+      <c r="D96" s="6">
         <f>D15/D14</f>
         <v/>
       </c>
-      <c r="E96" s="5">
+      <c r="E96" s="6">
         <f>E15/E14</f>
         <v/>
       </c>
-      <c r="F96" s="5">
+      <c r="F96" s="6">
         <f>F15/F14</f>
         <v/>
       </c>
-      <c r="G96" s="5">
+      <c r="G96" s="6">
         <f>G15/G14</f>
         <v/>
       </c>
-      <c r="H96" s="5">
+      <c r="H96" s="6">
         <f>H15/H14</f>
         <v/>
       </c>
-      <c r="I96" s="5">
+      <c r="I96" s="6">
         <f>I15/I14</f>
         <v/>
       </c>
-      <c r="J96" s="5">
+      <c r="J96" s="6">
         <f>J15/J14</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>利润留存</t>
         </is>
       </c>
-      <c r="D97" s="5">
+      <c r="D97" s="6">
         <f>D16/D14</f>
         <v/>
       </c>
-      <c r="E97" s="5">
+      <c r="E97" s="6">
         <f>E16/E14</f>
         <v/>
       </c>
-      <c r="F97" s="5">
+      <c r="F97" s="6">
         <f>F16/F14</f>
         <v/>
       </c>
-      <c r="G97" s="5">
+      <c r="G97" s="6">
         <f>G16/G14</f>
         <v/>
       </c>
-      <c r="H97" s="5">
+      <c r="H97" s="6">
         <f>H16/H14</f>
         <v/>
       </c>
-      <c r="I97" s="5">
+      <c r="I97" s="6">
         <f>I16/I14</f>
         <v/>
       </c>
-      <c r="J97" s="5">
+      <c r="J97" s="6">
         <f>J16/J14</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>营收YoY</t>
         </is>
       </c>
-      <c r="D99" s="5">
+      <c r="D99" s="6">
         <f>(D28-E28)/E28</f>
         <v/>
       </c>
-      <c r="E99" s="5">
+      <c r="E99" s="6">
         <f>(E28-F28)/F28</f>
         <v/>
       </c>
-      <c r="F99" s="5">
+      <c r="F99" s="6">
         <f>(F28-G28)/G28</f>
         <v/>
       </c>
-      <c r="G99" s="5">
+      <c r="G99" s="6">
         <f>(G28-H28)/H28</f>
         <v/>
       </c>
-      <c r="H99" s="5">
+      <c r="H99" s="6">
         <f>(H28-I28)/I28</f>
         <v/>
       </c>
-      <c r="I99" s="5">
+      <c r="I99" s="6">
         <f>(I28-J28)/J28</f>
         <v/>
       </c>
-      <c r="J99" s="6" t="n"/>
+      <c r="J99" s="7" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>业务净利润YoY</t>
         </is>
       </c>
-      <c r="D100" s="5">
+      <c r="D100" s="6">
         <f>(D59-E59)/E59</f>
         <v/>
       </c>
-      <c r="E100" s="5">
+      <c r="E100" s="6">
         <f>(E59-F59)/F59</f>
         <v/>
       </c>
-      <c r="F100" s="5">
+      <c r="F100" s="6">
         <f>(F59-G59)/G59</f>
         <v/>
       </c>
-      <c r="G100" s="5">
+      <c r="G100" s="6">
         <f>(G59-H59)/H59</f>
         <v/>
       </c>
-      <c r="H100" s="5">
+      <c r="H100" s="6">
         <f>(H59-I59)/I59</f>
         <v/>
       </c>
-      <c r="I100" s="5">
+      <c r="I100" s="6">
         <f>(I59-J59)/J59</f>
         <v/>
       </c>
-      <c r="J100" s="6" t="n"/>
+      <c r="J100" s="7" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>资产YoY</t>
         </is>
       </c>
-      <c r="D102" s="5">
+      <c r="D102" s="6">
         <f>(D2-E2)/E2</f>
         <v/>
       </c>
-      <c r="E102" s="5">
+      <c r="E102" s="6">
         <f>(E2-F2)/F2</f>
         <v/>
       </c>
-      <c r="F102" s="5">
+      <c r="F102" s="6">
         <f>(F2-G2)/G2</f>
         <v/>
       </c>
-      <c r="G102" s="5">
+      <c r="G102" s="6">
         <f>(G2-H2)/H2</f>
         <v/>
       </c>
-      <c r="H102" s="5">
+      <c r="H102" s="6">
         <f>(H2-I2)/I2</f>
         <v/>
       </c>
-      <c r="I102" s="5">
+      <c r="I102" s="6">
         <f>(I2-J2)/J2</f>
         <v/>
       </c>
-      <c r="J102" s="6" t="n"/>
+      <c r="J102" s="7" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="A103" s="5" t="inlineStr">
         <is>
           <t>现金</t>
         </is>
       </c>
-      <c r="D103" s="5">
+      <c r="D103" s="6">
         <f>(D3-E3)/E3</f>
         <v/>
       </c>
-      <c r="E103" s="5">
+      <c r="E103" s="6">
         <f>(E3-F3)/F3</f>
         <v/>
       </c>
-      <c r="F103" s="5">
+      <c r="F103" s="6">
         <f>(F3-G3)/G3</f>
         <v/>
       </c>
-      <c r="G103" s="5">
+      <c r="G103" s="6">
         <f>(G3-H3)/H3</f>
         <v/>
       </c>
-      <c r="H103" s="5">
+      <c r="H103" s="6">
         <f>(H3-I3)/I3</f>
         <v/>
       </c>
-      <c r="I103" s="5">
+      <c r="I103" s="6">
         <f>(I3-J3)/J3</f>
         <v/>
       </c>
-      <c r="J103" s="6" t="n"/>
+      <c r="J103" s="7" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>投资</t>
         </is>
       </c>
-      <c r="D104" s="5">
+      <c r="D104" s="6">
         <f>(D4-E4)/E4</f>
         <v/>
       </c>
-      <c r="E104" s="5">
+      <c r="E104" s="6">
         <f>(E4-F4)/F4</f>
         <v/>
       </c>
-      <c r="F104" s="5">
+      <c r="F104" s="6">
         <f>(F4-G4)/G4</f>
         <v/>
       </c>
-      <c r="G104" s="5">
+      <c r="G104" s="6">
         <f>(G4-H4)/H4</f>
         <v/>
       </c>
-      <c r="H104" s="5">
+      <c r="H104" s="6">
         <f>(H4-I4)/I4</f>
         <v/>
       </c>
-      <c r="I104" s="5">
+      <c r="I104" s="6">
         <f>(I4-J4)/J4</f>
         <v/>
       </c>
-      <c r="J104" s="6" t="n"/>
+      <c r="J104" s="7" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="inlineStr">
+      <c r="A105" s="5" t="inlineStr">
         <is>
           <t>运营资产</t>
         </is>
       </c>
-      <c r="D105" s="5">
+      <c r="D105" s="6">
         <f>(D5-E5)/E5</f>
         <v/>
       </c>
-      <c r="E105" s="5">
+      <c r="E105" s="6">
         <f>(E5-F5)/F5</f>
         <v/>
       </c>
-      <c r="F105" s="5">
+      <c r="F105" s="6">
         <f>(F5-G5)/G5</f>
         <v/>
       </c>
-      <c r="G105" s="5">
+      <c r="G105" s="6">
         <f>(G5-H5)/H5</f>
         <v/>
       </c>
-      <c r="H105" s="5">
+      <c r="H105" s="6">
         <f>(H5-I5)/I5</f>
         <v/>
       </c>
-      <c r="I105" s="5">
+      <c r="I105" s="6">
         <f>(I5-J5)/J5</f>
         <v/>
       </c>
-      <c r="J105" s="6" t="n"/>
+      <c r="J105" s="7" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="inlineStr">
+      <c r="A106" s="5" t="inlineStr">
         <is>
           <t>长期资产</t>
         </is>
       </c>
-      <c r="D106" s="5">
+      <c r="D106" s="6">
         <f>(D9-E9)/E9</f>
         <v/>
       </c>
-      <c r="E106" s="5">
+      <c r="E106" s="6">
         <f>(E9-F9)/F9</f>
         <v/>
       </c>
-      <c r="F106" s="5">
+      <c r="F106" s="6">
         <f>(F9-G9)/G9</f>
         <v/>
       </c>
-      <c r="G106" s="5">
+      <c r="G106" s="6">
         <f>(G9-H9)/H9</f>
         <v/>
       </c>
-      <c r="H106" s="5">
+      <c r="H106" s="6">
         <f>(H9-I9)/I9</f>
         <v/>
       </c>
-      <c r="I106" s="5">
+      <c r="I106" s="6">
         <f>(I9-J9)/J9</f>
         <v/>
       </c>
-      <c r="J106" s="6" t="n"/>
+      <c r="J106" s="7" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>权益YoY</t>
         </is>
       </c>
-      <c r="D107" s="5">
+      <c r="D107" s="6">
         <f>(D14-E14)/E14</f>
         <v/>
       </c>
-      <c r="E107" s="5">
+      <c r="E107" s="6">
         <f>(E14-F14)/F14</f>
         <v/>
       </c>
-      <c r="F107" s="5">
+      <c r="F107" s="6">
         <f>(F14-G14)/G14</f>
         <v/>
       </c>
-      <c r="G107" s="5">
+      <c r="G107" s="6">
         <f>(G14-H14)/H14</f>
         <v/>
       </c>
-      <c r="H107" s="5">
+      <c r="H107" s="6">
         <f>(H14-I14)/I14</f>
         <v/>
       </c>
-      <c r="I107" s="5">
+      <c r="I107" s="6">
         <f>(I14-J14)/J14</f>
         <v/>
       </c>
-      <c r="J107" s="6" t="n"/>
+      <c r="J107" s="7" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>资本投入</t>
         </is>
       </c>
-      <c r="D108" s="5">
+      <c r="D108" s="6">
         <f>(D15-E15)/E15</f>
         <v/>
       </c>
-      <c r="E108" s="5">
+      <c r="E108" s="6">
         <f>(E15-F15)/F15</f>
         <v/>
       </c>
-      <c r="F108" s="5">
+      <c r="F108" s="6">
         <f>(F15-G15)/G15</f>
         <v/>
       </c>
-      <c r="G108" s="5">
+      <c r="G108" s="6">
         <f>(G15-H15)/H15</f>
         <v/>
       </c>
-      <c r="H108" s="5">
+      <c r="H108" s="6">
         <f>(H15-I15)/I15</f>
         <v/>
       </c>
-      <c r="I108" s="5">
+      <c r="I108" s="6">
         <f>(I15-J15)/J15</f>
         <v/>
       </c>
-      <c r="J108" s="6" t="n"/>
+      <c r="J108" s="7" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="A109" s="5" t="inlineStr">
         <is>
           <t>未分配利润</t>
         </is>
       </c>
-      <c r="D109" s="5">
+      <c r="D109" s="6">
         <f>(D16-E16)/E16</f>
         <v/>
       </c>
-      <c r="E109" s="5">
+      <c r="E109" s="6">
         <f>(E16-F16)/F16</f>
         <v/>
       </c>
-      <c r="F109" s="5">
+      <c r="F109" s="6">
         <f>(F16-G16)/G16</f>
         <v/>
       </c>
-      <c r="G109" s="5">
+      <c r="G109" s="6">
         <f>(G16-H16)/H16</f>
         <v/>
       </c>
-      <c r="H109" s="5">
+      <c r="H109" s="6">
         <f>(H16-I16)/I16</f>
         <v/>
       </c>
-      <c r="I109" s="5">
+      <c r="I109" s="6">
         <f>(I16-J16)/J16</f>
         <v/>
       </c>
-      <c r="J109" s="6" t="n"/>
+      <c r="J109" s="7" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>负债YoY</t>
         </is>
       </c>
-      <c r="D110" s="5">
+      <c r="D110" s="6">
         <f>(D10-E10)/E10</f>
         <v/>
       </c>
-      <c r="E110" s="5">
+      <c r="E110" s="6">
         <f>(E10-F10)/F10</f>
         <v/>
       </c>
-      <c r="F110" s="5">
+      <c r="F110" s="6">
         <f>(F10-G10)/G10</f>
         <v/>
       </c>
-      <c r="G110" s="5">
+      <c r="G110" s="6">
         <f>(G10-H10)/H10</f>
         <v/>
       </c>
-      <c r="H110" s="5">
+      <c r="H110" s="6">
         <f>(H10-I10)/I10</f>
         <v/>
       </c>
-      <c r="I110" s="5">
+      <c r="I110" s="6">
         <f>(I10-J10)/J10</f>
         <v/>
       </c>
-      <c r="J110" s="6" t="n"/>
+      <c r="J110" s="7" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="A111" s="5" t="inlineStr">
         <is>
           <t>预收</t>
         </is>
       </c>
-      <c r="D111" s="5">
+      <c r="D111" s="6">
         <f>(D11-E11)/E11</f>
         <v/>
       </c>
-      <c r="E111" s="5">
+      <c r="E111" s="6">
         <f>(E11-F11)/F11</f>
         <v/>
       </c>
-      <c r="F111" s="5">
+      <c r="F111" s="6">
         <f>(F11-G11)/G11</f>
         <v/>
       </c>
-      <c r="G111" s="5">
+      <c r="G111" s="6">
         <f>(G11-H11)/H11</f>
         <v/>
       </c>
-      <c r="H111" s="5">
+      <c r="H111" s="6">
         <f>(H11-I11)/I11</f>
         <v/>
       </c>
-      <c r="I111" s="5">
+      <c r="I111" s="6">
         <f>(I11-J11)/J11</f>
         <v/>
       </c>
-      <c r="J111" s="6" t="n"/>
+      <c r="J111" s="7" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="inlineStr">
+      <c r="A112" s="5" t="inlineStr">
         <is>
           <t>应付</t>
         </is>
       </c>
-      <c r="D112" s="5">
+      <c r="D112" s="6">
         <f>(D12-E12)/E12</f>
         <v/>
       </c>
-      <c r="E112" s="5">
+      <c r="E112" s="6">
         <f>(E12-F12)/F12</f>
         <v/>
       </c>
-      <c r="F112" s="5">
+      <c r="F112" s="6">
         <f>(F12-G12)/G12</f>
         <v/>
       </c>
-      <c r="G112" s="5">
+      <c r="G112" s="6">
         <f>(G12-H12)/H12</f>
         <v/>
       </c>
-      <c r="H112" s="5">
+      <c r="H112" s="6">
         <f>(H12-I12)/I12</f>
         <v/>
       </c>
-      <c r="I112" s="5">
+      <c r="I112" s="6">
         <f>(I12-J12)/J12</f>
         <v/>
       </c>
-      <c r="J112" s="6" t="n"/>
+      <c r="J112" s="7" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="inlineStr">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>有息债务</t>
         </is>
       </c>
-      <c r="D113" s="5">
+      <c r="D113" s="6">
         <f>(D13-E13)/E13</f>
         <v/>
       </c>
-      <c r="E113" s="5">
+      <c r="E113" s="6">
         <f>(E13-F13)/F13</f>
         <v/>
       </c>
-      <c r="F113" s="5">
+      <c r="F113" s="6">
         <f>(F13-G13)/G13</f>
         <v/>
       </c>
-      <c r="G113" s="5">
+      <c r="G113" s="6">
         <f>(G13-H13)/H13</f>
         <v/>
       </c>
-      <c r="H113" s="5">
+      <c r="H113" s="6">
         <f>(H13-I13)/I13</f>
         <v/>
       </c>
-      <c r="I113" s="5">
+      <c r="I113" s="6">
         <f>(I13-J13)/J13</f>
         <v/>
       </c>
-      <c r="J113" s="6" t="n"/>
+      <c r="J113" s="7" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="A115" s="3" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="D115" s="5">
+      <c r="D115" s="6">
         <f>D59/D14</f>
         <v/>
       </c>
-      <c r="E115" s="5">
+      <c r="E115" s="6">
         <f>E59/E14</f>
         <v/>
       </c>
-      <c r="F115" s="5">
+      <c r="F115" s="6">
         <f>F59/F14</f>
         <v/>
       </c>
-      <c r="G115" s="5">
+      <c r="G115" s="6">
         <f>G59/G14</f>
         <v/>
       </c>
-      <c r="H115" s="5">
+      <c r="H115" s="6">
         <f>H59/H14</f>
         <v/>
       </c>
-      <c r="I115" s="5">
+      <c r="I115" s="6">
         <f>I59/I14</f>
         <v/>
       </c>
-      <c r="J115" s="5">
+      <c r="J115" s="6">
         <f>J59/J14</f>
         <v/>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+      <c r="A116" s="5" t="inlineStr">
         <is>
           <t>Net Proit</t>
         </is>
       </c>
-      <c r="D116" s="5">
+      <c r="D116" s="6">
         <f>D59/D28</f>
         <v/>
       </c>
-      <c r="E116" s="5">
+      <c r="E116" s="6">
         <f>E59/E28</f>
         <v/>
       </c>
-      <c r="F116" s="5">
+      <c r="F116" s="6">
         <f>F59/F28</f>
         <v/>
       </c>
-      <c r="G116" s="5">
+      <c r="G116" s="6">
         <f>G59/G28</f>
         <v/>
       </c>
-      <c r="H116" s="5">
+      <c r="H116" s="6">
         <f>H59/H28</f>
         <v/>
       </c>
-      <c r="I116" s="5">
+      <c r="I116" s="6">
         <f>I59/I28</f>
         <v/>
       </c>
-      <c r="J116" s="5">
+      <c r="J116" s="6">
         <f>J59/J28</f>
         <v/>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+      <c r="A117" s="5" t="inlineStr">
         <is>
           <t>主营收入/资产</t>
         </is>
       </c>
-      <c r="D117" s="5">
+      <c r="D117" s="6">
         <f>D28/D2</f>
         <v/>
       </c>
-      <c r="E117" s="5">
+      <c r="E117" s="6">
         <f>E28/E2</f>
         <v/>
       </c>
-      <c r="F117" s="5">
+      <c r="F117" s="6">
         <f>F28/F2</f>
         <v/>
       </c>
-      <c r="G117" s="5">
+      <c r="G117" s="6">
         <f>G28/G2</f>
         <v/>
       </c>
-      <c r="H117" s="5">
+      <c r="H117" s="6">
         <f>H28/H2</f>
         <v/>
       </c>
-      <c r="I117" s="5">
+      <c r="I117" s="6">
         <f>I28/I2</f>
         <v/>
       </c>
-      <c r="J117" s="5">
+      <c r="J117" s="6">
         <f>J28/J2</f>
         <v/>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="inlineStr">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>资产/资本</t>
         </is>
       </c>
-      <c r="D118" s="5">
+      <c r="D118" s="6">
         <f>D2/D14</f>
         <v/>
       </c>
-      <c r="E118" s="5">
+      <c r="E118" s="6">
         <f>E2/E14</f>
         <v/>
       </c>
-      <c r="F118" s="5">
+      <c r="F118" s="6">
         <f>F2/F14</f>
         <v/>
       </c>
-      <c r="G118" s="5">
+      <c r="G118" s="6">
         <f>G2/G14</f>
         <v/>
       </c>
-      <c r="H118" s="5">
+      <c r="H118" s="6">
         <f>H2/H14</f>
         <v/>
       </c>
-      <c r="I118" s="5">
+      <c r="I118" s="6">
         <f>I2/I14</f>
         <v/>
       </c>
-      <c r="J118" s="5">
+      <c r="J118" s="6">
         <f>J2/J14</f>
         <v/>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="A120" s="3" t="inlineStr">
         <is>
           <t>股息</t>
         </is>
       </c>
-      <c r="D120" s="3" t="n"/>
-      <c r="E120" s="3" t="n"/>
-      <c r="F120" s="3" t="n"/>
-      <c r="G120" s="3" t="n"/>
-      <c r="H120" s="3" t="n"/>
-      <c r="I120" s="3" t="n"/>
-      <c r="J120" s="3" t="n"/>
+      <c r="D120" s="4" t="n"/>
+      <c r="E120" s="4" t="n"/>
+      <c r="F120" s="4" t="n"/>
+      <c r="G120" s="4" t="n"/>
+      <c r="H120" s="4" t="n"/>
+      <c r="I120" s="4" t="n"/>
+      <c r="J120" s="4" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="D121" s="5">
+      <c r="D121" s="6">
         <f>D59/D26</f>
         <v/>
       </c>
-      <c r="E121" s="5">
+      <c r="E121" s="6">
         <f>E59/E26</f>
         <v/>
       </c>
-      <c r="F121" s="5">
+      <c r="F121" s="6">
         <f>F59/F26</f>
         <v/>
       </c>
-      <c r="G121" s="5">
+      <c r="G121" s="6">
         <f>G59/G26</f>
         <v/>
       </c>
-      <c r="H121" s="5">
+      <c r="H121" s="6">
         <f>H59/H26</f>
         <v/>
       </c>
-      <c r="I121" s="5">
+      <c r="I121" s="6">
         <f>I59/I26</f>
         <v/>
       </c>
-      <c r="J121" s="5">
+      <c r="J121" s="6">
         <f>J59/J26</f>
         <v/>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t>FPS</t>
         </is>
       </c>
-      <c r="D122" s="5">
+      <c r="D122" s="6">
         <f>D69/D26</f>
         <v/>
       </c>
-      <c r="E122" s="5">
+      <c r="E122" s="6">
         <f>E69/E26</f>
         <v/>
       </c>
-      <c r="F122" s="5">
+      <c r="F122" s="6">
         <f>F69/F26</f>
         <v/>
       </c>
-      <c r="G122" s="5">
+      <c r="G122" s="6">
         <f>G69/G26</f>
         <v/>
       </c>
-      <c r="H122" s="5">
+      <c r="H122" s="6">
         <f>H69/H26</f>
         <v/>
       </c>
-      <c r="I122" s="5">
+      <c r="I122" s="6">
         <f>I69/I26</f>
         <v/>
       </c>
-      <c r="J122" s="5">
+      <c r="J122" s="6">
         <f>J69/J26</f>
         <v/>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="A124" s="3" t="inlineStr">
         <is>
           <t>价格（H）</t>
         </is>
       </c>
-      <c r="D124" s="7" t="n"/>
-      <c r="E124" s="7" t="n"/>
-      <c r="F124" s="7" t="n"/>
-      <c r="G124" s="7" t="n"/>
-      <c r="H124" s="7" t="n"/>
-      <c r="I124" s="7" t="n"/>
-      <c r="J124" s="7" t="n"/>
+      <c r="D124" s="8" t="n"/>
+      <c r="E124" s="8" t="n"/>
+      <c r="F124" s="8" t="n"/>
+      <c r="G124" s="8" t="n"/>
+      <c r="H124" s="8" t="n"/>
+      <c r="I124" s="8" t="n"/>
+      <c r="J124" s="8" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="A125" s="3" t="inlineStr">
         <is>
           <t>价格（L）</t>
         </is>
       </c>
-      <c r="D125" s="7" t="n"/>
-      <c r="E125" s="7" t="n"/>
-      <c r="F125" s="7" t="n"/>
-      <c r="G125" s="7" t="n"/>
-      <c r="H125" s="7" t="n"/>
-      <c r="I125" s="7" t="n"/>
-      <c r="J125" s="7" t="n"/>
+      <c r="D125" s="8" t="n"/>
+      <c r="E125" s="8" t="n"/>
+      <c r="F125" s="8" t="n"/>
+      <c r="G125" s="8" t="n"/>
+      <c r="H125" s="8" t="n"/>
+      <c r="I125" s="8" t="n"/>
+      <c r="J125" s="8" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="D126" s="5">
+      <c r="D126" s="6">
         <f>D124/(D59/D26)</f>
         <v/>
       </c>
-      <c r="E126" s="5">
+      <c r="E126" s="6">
         <f>E124/(E59/E26)</f>
         <v/>
       </c>
-      <c r="F126" s="5">
+      <c r="F126" s="6">
         <f>F124/(F59/F26)</f>
         <v/>
       </c>
-      <c r="G126" s="5">
+      <c r="G126" s="6">
         <f>G124/(G59/G26)</f>
         <v/>
       </c>
-      <c r="H126" s="5">
+      <c r="H126" s="6">
         <f>H124/(H59/H26)</f>
         <v/>
       </c>
-      <c r="I126" s="5">
+      <c r="I126" s="6">
         <f>I124/(I59/I26)</f>
         <v/>
       </c>
-      <c r="J126" s="5">
+      <c r="J126" s="6">
         <f>J124/(J59/J26)</f>
         <v/>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="A127" s="3" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="D127" s="5">
+      <c r="D127" s="6">
         <f>D125/(D59/D26)</f>
         <v/>
       </c>
-      <c r="E127" s="5">
+      <c r="E127" s="6">
         <f>E125/(E59/E26)</f>
         <v/>
       </c>
-      <c r="F127" s="5">
+      <c r="F127" s="6">
         <f>F125/(F59/F26)</f>
         <v/>
       </c>
-      <c r="G127" s="5">
+      <c r="G127" s="6">
         <f>G125/(G59/G26)</f>
         <v/>
       </c>
-      <c r="H127" s="5">
+      <c r="H127" s="6">
         <f>H125/(H59/H26)</f>
         <v/>
       </c>
-      <c r="I127" s="5">
+      <c r="I127" s="6">
         <f>I125/(I59/I26)</f>
         <v/>
       </c>
-      <c r="J127" s="5">
+      <c r="J127" s="6">
         <f>J125/(J59/J26)</f>
         <v/>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="A128" s="3" t="inlineStr">
         <is>
           <t>股息率</t>
         </is>
       </c>
-      <c r="D128" s="5">
+      <c r="D128" s="6">
         <f>(D17/D26)/D124</f>
         <v/>
       </c>
-      <c r="E128" s="5">
+      <c r="E128" s="6">
         <f>(E17/E26)/E124</f>
         <v/>
       </c>
-      <c r="F128" s="5">
+      <c r="F128" s="6">
         <f>(F17/F26)/F124</f>
         <v/>
       </c>
-      <c r="G128" s="5">
+      <c r="G128" s="6">
         <f>(G17/G26)/G124</f>
         <v/>
       </c>
-      <c r="H128" s="5">
+      <c r="H128" s="6">
         <f>(H17/H26)/H124</f>
         <v/>
       </c>
-      <c r="I128" s="5">
+      <c r="I128" s="6">
         <f>(I17/I26)/I124</f>
         <v/>
       </c>
-      <c r="J128" s="5">
+      <c r="J128" s="6">
         <f>(J17/J26)/J124</f>
         <v/>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="A129" s="3" t="inlineStr">
         <is>
           <t>股息率</t>
         </is>
       </c>
-      <c r="D129" s="5">
+      <c r="D129" s="6">
         <f>(D17/D26)/D125</f>
         <v/>
       </c>
-      <c r="E129" s="5">
+      <c r="E129" s="6">
         <f>(E17/E26)/E125</f>
         <v/>
       </c>
-      <c r="F129" s="5">
+      <c r="F129" s="6">
         <f>(F17/F26)/F125</f>
         <v/>
       </c>
-      <c r="G129" s="5">
+      <c r="G129" s="6">
         <f>(G17/G26)/G125</f>
         <v/>
       </c>
-      <c r="H129" s="5">
+      <c r="H129" s="6">
         <f>(H17/H26)/H125</f>
         <v/>
       </c>
-      <c r="I129" s="5">
+      <c r="I129" s="6">
         <f>(I17/I26)/I125</f>
         <v/>
       </c>
-      <c r="J129" s="5">
+      <c r="J129" s="6">
         <f>(J17/J26)/J125</f>
         <v/>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="A132" s="3" t="inlineStr">
         <is>
           <t>市值</t>
         </is>
       </c>
-      <c r="D132" s="5">
+      <c r="D132" s="6">
         <f>D124*D26</f>
         <v/>
       </c>
-      <c r="E132" s="5">
+      <c r="E132" s="6">
         <f>E124*E26</f>
         <v/>
       </c>
-      <c r="F132" s="5">
+      <c r="F132" s="6">
         <f>F124*F26</f>
         <v/>
       </c>
-      <c r="G132" s="5">
+      <c r="G132" s="6">
         <f>G124*G26</f>
         <v/>
       </c>
-      <c r="H132" s="5">
+      <c r="H132" s="6">
         <f>H124*H26</f>
         <v/>
       </c>
-      <c r="I132" s="5">
+      <c r="I132" s="6">
         <f>I124*I26</f>
         <v/>
       </c>
-      <c r="J132" s="5">
+      <c r="J132" s="6">
         <f>J124*J26</f>
         <v/>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="A133" s="3" t="inlineStr">
         <is>
           <t>市值</t>
         </is>
       </c>
-      <c r="D133" s="5">
+      <c r="D133" s="6">
         <f>D125*D26</f>
         <v/>
       </c>
-      <c r="E133" s="5">
+      <c r="E133" s="6">
         <f>E125*E26</f>
         <v/>
       </c>
-      <c r="F133" s="5">
+      <c r="F133" s="6">
         <f>F125*F26</f>
         <v/>
       </c>
-      <c r="G133" s="5">
+      <c r="G133" s="6">
         <f>G125*G26</f>
         <v/>
       </c>
-      <c r="H133" s="5">
+      <c r="H133" s="6">
         <f>H125*H26</f>
         <v/>
       </c>
-      <c r="I133" s="5">
+      <c r="I133" s="6">
         <f>I125*I26</f>
         <v/>
       </c>
-      <c r="J133" s="5">
+      <c r="J133" s="6">
         <f>J125*J26</f>
         <v/>
       </c>

--- a/examples/福耀玻璃_Beta04_完整分析.xlsx
+++ b/examples/福耀玻璃_Beta04_完整分析.xlsx
@@ -1222,25 +1222,25 @@
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5746301975</v>
+        <v>6032289023</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5427862941</v>
+        <v>5667759562</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4742246146</v>
+        <v>4967587622</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4092374443</v>
+        <v>4297003585</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4366570267</v>
+        <v>4564753107</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4480060059</v>
+        <v>4677876806</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4418465472</v>
+        <v>4621537694</v>
       </c>
     </row>
     <row r="31">
@@ -1330,497 +1330,490 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
+          <t>税金及附加</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>285987048</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>239896621</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>225341476</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>204629142</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>198182840</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>197816747</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>203072222</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t>损耗</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D35" s="4" t="n">
         <v>-98548679</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E35" s="4" t="n">
         <v>-220776671</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F35" s="4" t="n">
         <v>-150481522</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>-23928049</v>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>38157119</v>
       </c>
-      <c r="I34" s="4" t="n">
+      <c r="I35" s="4" t="n">
         <v>-20103858</v>
       </c>
-      <c r="J34" s="4" t="n">
+      <c r="J35" s="4" t="n">
         <v>-51746308</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>其他收益</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>400415185</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>262917177</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>215071387</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>242337506</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>352820556</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>181754102</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>146750220</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>现金收益</t>
+          <t>其他收益</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>924966003</v>
+        <v>400415185</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>602544066</v>
+        <v>262917177</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>231495735</v>
+        <v>215071387</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>195413923</v>
+        <v>242337506</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>348762592</v>
+        <v>352820556</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>336984661</v>
+        <v>181754102</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>335452093</v>
+        <v>146750220</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>股权收益</t>
+          <t>现金收益</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>-15801862</v>
+        <v>924966003</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>4290148</v>
+        <v>602544066</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>20962737</v>
+        <v>231495735</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>26975045</v>
+        <v>195413923</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>11843754</v>
+        <v>348762592</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>-5932899</v>
+        <v>336984661</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>667776495</v>
+        <v>335452093</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>利息支出</t>
+          <t>股权收益</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>288507082</v>
+        <v>-15801862</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>288319603</v>
+        <v>4290148</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>288122259</v>
+        <v>20962737</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>318940791</v>
+        <v>26975045</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>354752403</v>
+        <v>11843754</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>432679520</v>
+        <v>-5932899</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>376230473</v>
+        <v>667776495</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>财务费用</t>
+          <t>利息支出</t>
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>35964048</v>
+        <v>288507082</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>-361719066</v>
+        <v>288319603</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>-1036725297</v>
+        <v>288122259</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>536834250</v>
+        <v>318940791</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>429822814</v>
+        <v>354752403</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>-127469129</v>
+        <v>432679520</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>-250823052</v>
+        <v>376230473</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
+          <t>财务费用</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>35964048</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>-361719066</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>-1036725297</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>536834250</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>429822814</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>-127469129</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>-250823052</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
           <t>其他业务</t>
         </is>
       </c>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>收入</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>541228588</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>510819743</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>447775365</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>341929292</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>265304196</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>338789268</v>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>341146746</v>
-      </c>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>541228588</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>510819743</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>447775365</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>341929292</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>265304196</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>338789268</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>341146746</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
           <t>成本</t>
         </is>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D43" s="4" t="n">
         <v>108449502</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E43" s="4" t="n">
         <v>114234160</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F43" s="4" t="n">
         <v>125334935</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G43" s="4" t="n">
         <v>89204424</v>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="H43" s="4" t="n">
         <v>97335416</v>
       </c>
-      <c r="I42" s="4" t="n">
+      <c r="I43" s="4" t="n">
         <v>136627509</v>
       </c>
-      <c r="J42" s="4" t="n">
+      <c r="J43" s="4" t="n">
         <v>114387863</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>营业外</t>
         </is>
       </c>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
-      <c r="J43" s="4" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>收入</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>35905331</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>49843149</v>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>80855034</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>217974835</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>57628048</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>109494454</v>
-      </c>
-      <c r="J44" s="4" t="n">
-        <v>60687441</v>
-      </c>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="n"/>
+      <c r="J44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>35905331</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>49843149</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>80855034</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>217974835</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>57628048</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>109494454</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>60687441</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
           <t>成本</t>
         </is>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D46" s="4" t="n">
         <v>120136061</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E46" s="4" t="n">
         <v>125106357</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F46" s="4" t="n">
         <v>163122132</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G46" s="4" t="n">
         <v>161162665</v>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="H46" s="4" t="n">
         <v>214664627</v>
       </c>
-      <c r="I45" s="4" t="n">
+      <c r="I46" s="4" t="n">
         <v>294294341</v>
       </c>
-      <c r="J45" s="4" t="n">
+      <c r="J46" s="4" t="n">
         <v>71545321</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>所得税</t>
         </is>
       </c>
-      <c r="D46" s="4" t="n">
+      <c r="D47" s="4" t="n">
         <v>1486781220</v>
       </c>
-      <c r="E46" s="4" t="n">
+      <c r="E47" s="4" t="n">
         <v>1086913641</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="F47" s="4" t="n">
         <v>826310042</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>675861301</v>
       </c>
-      <c r="H46" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>511144107</v>
       </c>
-      <c r="I46" s="4" t="n">
+      <c r="I47" s="4" t="n">
         <v>332955880</v>
       </c>
-      <c r="J46" s="4" t="n">
+      <c r="J47" s="4" t="n">
         <v>855187629</v>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>盈利结构</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="4" t="n"/>
-      <c r="G49" s="4" t="n"/>
-      <c r="H49" s="4" t="n"/>
-      <c r="I49" s="4" t="n"/>
-      <c r="J49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
+          <t>盈利结构</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
           <t>主营收入</t>
         </is>
       </c>
-      <c r="D50" s="6">
+      <c r="D51" s="6">
         <f>D28</f>
         <v/>
       </c>
-      <c r="E50" s="6">
+      <c r="E51" s="6">
         <f>E28</f>
         <v/>
       </c>
-      <c r="F50" s="6">
+      <c r="F51" s="6">
         <f>F28</f>
         <v/>
       </c>
-      <c r="G50" s="6">
+      <c r="G51" s="6">
         <f>G28</f>
         <v/>
       </c>
-      <c r="H50" s="6">
+      <c r="H51" s="6">
         <f>H28</f>
         <v/>
       </c>
-      <c r="I50" s="6">
+      <c r="I51" s="6">
         <f>I28</f>
         <v/>
       </c>
-      <c r="J50" s="6">
+      <c r="J51" s="6">
         <f>J28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>主营成本</t>
-        </is>
-      </c>
-      <c r="D51" s="6">
-        <f>D29</f>
-        <v/>
-      </c>
-      <c r="E51" s="6">
-        <f>E29</f>
-        <v/>
-      </c>
-      <c r="F51" s="6">
-        <f>F29</f>
-        <v/>
-      </c>
-      <c r="G51" s="6">
-        <f>G29</f>
-        <v/>
-      </c>
-      <c r="H51" s="6">
-        <f>H29</f>
-        <v/>
-      </c>
-      <c r="I51" s="6">
-        <f>I29</f>
-        <v/>
-      </c>
-      <c r="J51" s="6">
-        <f>J29</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>费用</t>
+          <t>主营成本</t>
         </is>
       </c>
       <c r="D52" s="6">
-        <f>D30</f>
+        <f>D29</f>
         <v/>
       </c>
       <c r="E52" s="6">
-        <f>E30</f>
+        <f>E29</f>
         <v/>
       </c>
       <c r="F52" s="6">
-        <f>F30</f>
+        <f>F29</f>
         <v/>
       </c>
       <c r="G52" s="6">
-        <f>G30</f>
+        <f>G29</f>
         <v/>
       </c>
       <c r="H52" s="6">
-        <f>H30</f>
+        <f>H29</f>
         <v/>
       </c>
       <c r="I52" s="6">
-        <f>I30</f>
+        <f>I29</f>
         <v/>
       </c>
       <c r="J52" s="6">
-        <f>J30</f>
+        <f>J29</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>损耗</t>
+          <t>费用</t>
         </is>
       </c>
       <c r="D53" s="6">
-        <f>D34</f>
+        <f>D30</f>
         <v/>
       </c>
       <c r="E53" s="6">
-        <f>E34</f>
+        <f>E30</f>
         <v/>
       </c>
       <c r="F53" s="6">
-        <f>F34</f>
+        <f>F30</f>
         <v/>
       </c>
       <c r="G53" s="6">
-        <f>G34</f>
+        <f>G30</f>
         <v/>
       </c>
       <c r="H53" s="6">
-        <f>H34</f>
+        <f>H30</f>
         <v/>
       </c>
       <c r="I53" s="6">
-        <f>I34</f>
+        <f>I30</f>
         <v/>
       </c>
       <c r="J53" s="6">
-        <f>J34</f>
+        <f>J30</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>其他收益</t>
+          <t>损耗</t>
         </is>
       </c>
       <c r="D54" s="6">
@@ -1855,7 +1848,7 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>现金收益</t>
+          <t>其他收益</t>
         </is>
       </c>
       <c r="D55" s="6">
@@ -1890,42 +1883,42 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>利息支出</t>
+          <t>现金收益</t>
         </is>
       </c>
       <c r="D56" s="6">
-        <f>D38</f>
+        <f>D37</f>
         <v/>
       </c>
       <c r="E56" s="6">
-        <f>E38</f>
+        <f>E37</f>
         <v/>
       </c>
       <c r="F56" s="6">
-        <f>F38</f>
+        <f>F37</f>
         <v/>
       </c>
       <c r="G56" s="6">
-        <f>G38</f>
+        <f>G37</f>
         <v/>
       </c>
       <c r="H56" s="6">
-        <f>H38</f>
+        <f>H37</f>
         <v/>
       </c>
       <c r="I56" s="6">
-        <f>I38</f>
+        <f>I37</f>
         <v/>
       </c>
       <c r="J56" s="6">
-        <f>J38</f>
+        <f>J37</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>财务费用</t>
+          <t>利息支出</t>
         </is>
       </c>
       <c r="D57" s="6">
@@ -1960,1338 +1953,1341 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
+          <t>财务费用</t>
+        </is>
+      </c>
+      <c r="D58" s="6">
+        <f>D40</f>
+        <v/>
+      </c>
+      <c r="E58" s="6">
+        <f>E40</f>
+        <v/>
+      </c>
+      <c r="F58" s="6">
+        <f>F40</f>
+        <v/>
+      </c>
+      <c r="G58" s="6">
+        <f>G40</f>
+        <v/>
+      </c>
+      <c r="H58" s="6">
+        <f>H40</f>
+        <v/>
+      </c>
+      <c r="I58" s="6">
+        <f>I40</f>
+        <v/>
+      </c>
+      <c r="J58" s="6">
+        <f>J40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
           <t>所得税</t>
         </is>
       </c>
-      <c r="D58" s="6">
-        <f>D46</f>
-        <v/>
-      </c>
-      <c r="E58" s="6">
-        <f>E46</f>
-        <v/>
-      </c>
-      <c r="F58" s="6">
-        <f>F46</f>
-        <v/>
-      </c>
-      <c r="G58" s="6">
-        <f>G46</f>
-        <v/>
-      </c>
-      <c r="H58" s="6">
-        <f>H46</f>
-        <v/>
-      </c>
-      <c r="I58" s="6">
-        <f>I46</f>
-        <v/>
-      </c>
-      <c r="J58" s="6">
-        <f>J46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="D59" s="6">
+        <f>D47</f>
+        <v/>
+      </c>
+      <c r="E59" s="6">
+        <f>E47</f>
+        <v/>
+      </c>
+      <c r="F59" s="6">
+        <f>F47</f>
+        <v/>
+      </c>
+      <c r="G59" s="6">
+        <f>G47</f>
+        <v/>
+      </c>
+      <c r="H59" s="6">
+        <f>H47</f>
+        <v/>
+      </c>
+      <c r="I59" s="6">
+        <f>I47</f>
+        <v/>
+      </c>
+      <c r="J59" s="6">
+        <f>J47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>业务利润</t>
         </is>
       </c>
-      <c r="D59" s="6">
-        <f>D50-D51-D52+D53+D54+D55-D56-D57-D58</f>
-        <v/>
-      </c>
-      <c r="E59" s="6">
-        <f>E50-E51-E52+E53+E54+E55-E56-E57-E58</f>
-        <v/>
-      </c>
-      <c r="F59" s="6">
-        <f>F50-F51-F52+F53+F54+F55-F56-F57-F58</f>
-        <v/>
-      </c>
-      <c r="G59" s="6">
-        <f>G50-G51-G52+G53+G54+G55-G56-G57-G58</f>
-        <v/>
-      </c>
-      <c r="H59" s="6">
-        <f>H50-H51-H52+H53+H54+H55-H56-H57-H58</f>
-        <v/>
-      </c>
-      <c r="I59" s="6">
-        <f>I50-I51-I52+I53+I54+I55-I56-I57-I58</f>
-        <v/>
-      </c>
-      <c r="J59" s="6">
-        <f>J50-J51-J52+J53+J54+J55-J56-J57-J58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>股权收益</t>
-        </is>
-      </c>
       <c r="D60" s="6">
-        <f>D37</f>
+        <f>D51-D52-D53+D54+D55+D56-D57-D58-D59</f>
         <v/>
       </c>
       <c r="E60" s="6">
-        <f>E37</f>
+        <f>E51-E52-E53+E54+E55+E56-E57-E58-E59</f>
         <v/>
       </c>
       <c r="F60" s="6">
-        <f>F37</f>
+        <f>F51-F52-F53+F54+F55+F56-F57-F58-F59</f>
         <v/>
       </c>
       <c r="G60" s="6">
-        <f>G37</f>
+        <f>G51-G52-G53+G54+G55+G56-G57-G58-G59</f>
         <v/>
       </c>
       <c r="H60" s="6">
-        <f>H37</f>
+        <f>H51-H52-H53+H54+H55+H56-H57-H58-H59</f>
         <v/>
       </c>
       <c r="I60" s="6">
-        <f>I37</f>
+        <f>I51-I52-I53+I54+I55+I56-I57-I58-I59</f>
         <v/>
       </c>
       <c r="J60" s="6">
-        <f>J37</f>
+        <f>J51-J52-J53+J54+J55+J56-J57-J58-J59</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>其他业务利润</t>
+          <t>股权收益</t>
         </is>
       </c>
       <c r="D61" s="6">
-        <f>D41-D42</f>
+        <f>D38</f>
         <v/>
       </c>
       <c r="E61" s="6">
-        <f>E41-E42</f>
+        <f>E38</f>
         <v/>
       </c>
       <c r="F61" s="6">
-        <f>F41-F42</f>
+        <f>F38</f>
         <v/>
       </c>
       <c r="G61" s="6">
-        <f>G41-G42</f>
+        <f>G38</f>
         <v/>
       </c>
       <c r="H61" s="6">
-        <f>H41-H42</f>
+        <f>H38</f>
         <v/>
       </c>
       <c r="I61" s="6">
-        <f>I41-I42</f>
+        <f>I38</f>
         <v/>
       </c>
       <c r="J61" s="6">
-        <f>J41-J42</f>
+        <f>J38</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>营业外利润</t>
+          <t>其他业务利润</t>
         </is>
       </c>
       <c r="D62" s="6">
-        <f>D44-D45</f>
+        <f>D42-D43</f>
         <v/>
       </c>
       <c r="E62" s="6">
-        <f>E44-E45</f>
+        <f>E42-E43</f>
         <v/>
       </c>
       <c r="F62" s="6">
-        <f>F44-F45</f>
+        <f>F42-F43</f>
         <v/>
       </c>
       <c r="G62" s="6">
-        <f>G44-G45</f>
+        <f>G42-G43</f>
         <v/>
       </c>
       <c r="H62" s="6">
-        <f>H44-H45</f>
+        <f>H42-H43</f>
         <v/>
       </c>
       <c r="I62" s="6">
-        <f>I44-I45</f>
+        <f>I42-I43</f>
         <v/>
       </c>
       <c r="J62" s="6">
-        <f>J44-J45</f>
+        <f>J42-J43</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>净利润</t>
+          <t>营业外利润</t>
         </is>
       </c>
       <c r="D63" s="6">
-        <f>D59+D60+D61+D62</f>
+        <f>D45-D46</f>
         <v/>
       </c>
       <c r="E63" s="6">
-        <f>E59+E60+E61+E62</f>
+        <f>E45-E46</f>
         <v/>
       </c>
       <c r="F63" s="6">
-        <f>F59+F60+F61+F62</f>
+        <f>F45-F46</f>
         <v/>
       </c>
       <c r="G63" s="6">
-        <f>G59+G60+G61+G62</f>
+        <f>G45-G46</f>
         <v/>
       </c>
       <c r="H63" s="6">
-        <f>H59+H60+H61+H62</f>
+        <f>H45-H46</f>
         <v/>
       </c>
       <c r="I63" s="6">
-        <f>I59+I60+I61+I62</f>
+        <f>I45-I46</f>
         <v/>
       </c>
       <c r="J63" s="6">
-        <f>J59+J60+J61+J62</f>
+        <f>J45-J46</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
+          <t>净利润</t>
+        </is>
+      </c>
+      <c r="D64" s="6">
+        <f>D60+D61+D62+D63</f>
+        <v/>
+      </c>
+      <c r="E64" s="6">
+        <f>E60+E61+E62+E63</f>
+        <v/>
+      </c>
+      <c r="F64" s="6">
+        <f>F60+F61+F62+F63</f>
+        <v/>
+      </c>
+      <c r="G64" s="6">
+        <f>G60+G61+G62+G63</f>
+        <v/>
+      </c>
+      <c r="H64" s="6">
+        <f>H60+H61+H62+H63</f>
+        <v/>
+      </c>
+      <c r="I64" s="6">
+        <f>I60+I61+I62+I63</f>
+        <v/>
+      </c>
+      <c r="J64" s="6">
+        <f>J60+J61+J62+J63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
           <t>分红</t>
         </is>
       </c>
-      <c r="D64" s="6">
+      <c r="D65" s="6">
         <f>D17</f>
         <v/>
       </c>
-      <c r="E64" s="6">
+      <c r="E65" s="6">
         <f>E17</f>
         <v/>
       </c>
-      <c r="F64" s="6">
+      <c r="F65" s="6">
         <f>F17</f>
         <v/>
       </c>
-      <c r="G64" s="6">
+      <c r="G65" s="6">
         <f>G17</f>
         <v/>
       </c>
-      <c r="H64" s="6">
+      <c r="H65" s="6">
         <f>H17</f>
         <v/>
       </c>
-      <c r="I64" s="6">
+      <c r="I65" s="6">
         <f>I17</f>
         <v/>
       </c>
-      <c r="J64" s="6">
+      <c r="J65" s="6">
         <f>J17</f>
         <v/>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>利润留存</t>
         </is>
       </c>
-      <c r="D65" s="6">
-        <f>D63-D64</f>
-        <v/>
-      </c>
-      <c r="E65" s="6">
-        <f>E63-E64</f>
-        <v/>
-      </c>
-      <c r="F65" s="6">
-        <f>F63-F64</f>
-        <v/>
-      </c>
-      <c r="G65" s="6">
-        <f>G63-G64</f>
-        <v/>
-      </c>
-      <c r="H65" s="6">
-        <f>H63-H64</f>
-        <v/>
-      </c>
-      <c r="I65" s="6">
-        <f>I63-I64</f>
-        <v/>
-      </c>
-      <c r="J65" s="6">
-        <f>J63-J64</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>折旧摊销</t>
-        </is>
-      </c>
       <c r="D66" s="6">
-        <f>D23</f>
+        <f>D64-D65</f>
         <v/>
       </c>
       <c r="E66" s="6">
-        <f>E23</f>
+        <f>E64-E65</f>
         <v/>
       </c>
       <c r="F66" s="6">
-        <f>F23</f>
+        <f>F64-F65</f>
         <v/>
       </c>
       <c r="G66" s="6">
-        <f>G23</f>
+        <f>G64-G65</f>
         <v/>
       </c>
       <c r="H66" s="6">
-        <f>H23</f>
+        <f>H64-H65</f>
         <v/>
       </c>
       <c r="I66" s="6">
-        <f>I23</f>
+        <f>I64-I65</f>
         <v/>
       </c>
       <c r="J66" s="6">
-        <f>J23</f>
+        <f>J64-J65</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
+          <t>折旧摊销</t>
+        </is>
+      </c>
+      <c r="D67" s="6">
+        <f>D23</f>
+        <v/>
+      </c>
+      <c r="E67" s="6">
+        <f>E23</f>
+        <v/>
+      </c>
+      <c r="F67" s="6">
+        <f>F23</f>
+        <v/>
+      </c>
+      <c r="G67" s="6">
+        <f>G23</f>
+        <v/>
+      </c>
+      <c r="H67" s="6">
+        <f>H23</f>
+        <v/>
+      </c>
+      <c r="I67" s="6">
+        <f>I23</f>
+        <v/>
+      </c>
+      <c r="J67" s="6">
+        <f>J23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
           <t>CAPEX</t>
         </is>
       </c>
-      <c r="D67" s="6">
+      <c r="D68" s="6">
         <f>D24</f>
         <v/>
       </c>
-      <c r="E67" s="6">
+      <c r="E68" s="6">
         <f>E24</f>
         <v/>
       </c>
-      <c r="F67" s="6">
+      <c r="F68" s="6">
         <f>F24</f>
         <v/>
       </c>
-      <c r="G67" s="6">
+      <c r="G68" s="6">
         <f>G24</f>
         <v/>
       </c>
-      <c r="H67" s="6">
+      <c r="H68" s="6">
         <f>H24</f>
         <v/>
       </c>
-      <c r="I67" s="6">
+      <c r="I68" s="6">
         <f>I24</f>
         <v/>
       </c>
-      <c r="J67" s="6">
+      <c r="J68" s="6">
         <f>J24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>现金留存</t>
-        </is>
-      </c>
-      <c r="D68" s="6">
-        <f>D65+D66-D67</f>
-        <v/>
-      </c>
-      <c r="E68" s="6">
-        <f>E65+E66-E67</f>
-        <v/>
-      </c>
-      <c r="F68" s="6">
-        <f>F65+F66-F67</f>
-        <v/>
-      </c>
-      <c r="G68" s="6">
-        <f>G65+G66-G67</f>
-        <v/>
-      </c>
-      <c r="H68" s="6">
-        <f>H65+H66-H67</f>
-        <v/>
-      </c>
-      <c r="I68" s="6">
-        <f>I65+I66-I67</f>
-        <v/>
-      </c>
-      <c r="J68" s="6">
-        <f>J65+J66-J67</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
+          <t>现金留存</t>
+        </is>
+      </c>
+      <c r="D69" s="6">
+        <f>D66+D67-D68</f>
+        <v/>
+      </c>
+      <c r="E69" s="6">
+        <f>E66+E67-E68</f>
+        <v/>
+      </c>
+      <c r="F69" s="6">
+        <f>F66+F67-F68</f>
+        <v/>
+      </c>
+      <c r="G69" s="6">
+        <f>G66+G67-G68</f>
+        <v/>
+      </c>
+      <c r="H69" s="6">
+        <f>H66+H67-H68</f>
+        <v/>
+      </c>
+      <c r="I69" s="6">
+        <f>I66+I67-I68</f>
+        <v/>
+      </c>
+      <c r="J69" s="6">
+        <f>J66+J67-J68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
           <t>业务现金</t>
         </is>
       </c>
-      <c r="D69" s="6">
-        <f>D59+D66-D67</f>
-        <v/>
-      </c>
-      <c r="E69" s="6">
-        <f>E59+E66-E67</f>
-        <v/>
-      </c>
-      <c r="F69" s="6">
-        <f>F59+F66-F67</f>
-        <v/>
-      </c>
-      <c r="G69" s="6">
-        <f>G59+G66-G67</f>
-        <v/>
-      </c>
-      <c r="H69" s="6">
-        <f>H59+H66-H67</f>
-        <v/>
-      </c>
-      <c r="I69" s="6">
-        <f>I59+I66-I67</f>
-        <v/>
-      </c>
-      <c r="J69" s="6">
-        <f>J59+J66-J67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>经营周转</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="n"/>
-      <c r="E71" s="4" t="n"/>
-      <c r="F71" s="4" t="n"/>
-      <c r="G71" s="4" t="n"/>
-      <c r="H71" s="4" t="n"/>
-      <c r="I71" s="4" t="n"/>
-      <c r="J71" s="4" t="n"/>
+      <c r="D70" s="6">
+        <f>D60+D67-D68</f>
+        <v/>
+      </c>
+      <c r="E70" s="6">
+        <f>E60+E67-E68</f>
+        <v/>
+      </c>
+      <c r="F70" s="6">
+        <f>F60+F67-F68</f>
+        <v/>
+      </c>
+      <c r="G70" s="6">
+        <f>G60+G67-G68</f>
+        <v/>
+      </c>
+      <c r="H70" s="6">
+        <f>H60+H67-H68</f>
+        <v/>
+      </c>
+      <c r="I70" s="6">
+        <f>I60+I67-I68</f>
+        <v/>
+      </c>
+      <c r="J70" s="6">
+        <f>J60+J67-J68</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>毛利率</t>
-        </is>
-      </c>
-      <c r="D72" s="6">
-        <f>(D28-D29)/D28</f>
-        <v/>
-      </c>
-      <c r="E72" s="6">
-        <f>(E28-E29)/E28</f>
-        <v/>
-      </c>
-      <c r="F72" s="6">
-        <f>(F28-F29)/F28</f>
-        <v/>
-      </c>
-      <c r="G72" s="6">
-        <f>(G28-G29)/G28</f>
-        <v/>
-      </c>
-      <c r="H72" s="6">
-        <f>(H28-H29)/H28</f>
-        <v/>
-      </c>
-      <c r="I72" s="6">
-        <f>(I28-I29)/I28</f>
-        <v/>
-      </c>
-      <c r="J72" s="6">
-        <f>(J28-J29)/J28</f>
-        <v/>
-      </c>
+          <t>经营周转</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="n"/>
+      <c r="G72" s="4" t="n"/>
+      <c r="H72" s="4" t="n"/>
+      <c r="I72" s="4" t="n"/>
+      <c r="J72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>费率</t>
+          <t>毛利率</t>
         </is>
       </c>
       <c r="D73" s="6">
-        <f>D30/D28</f>
+        <f>(D28-D29)/D28</f>
         <v/>
       </c>
       <c r="E73" s="6">
-        <f>E30/E28</f>
+        <f>(E28-E29)/E28</f>
         <v/>
       </c>
       <c r="F73" s="6">
-        <f>F30/F28</f>
+        <f>(F28-F29)/F28</f>
         <v/>
       </c>
       <c r="G73" s="6">
-        <f>G30/G28</f>
+        <f>(G28-G29)/G28</f>
         <v/>
       </c>
       <c r="H73" s="6">
-        <f>H30/H28</f>
+        <f>(H28-H29)/H28</f>
         <v/>
       </c>
       <c r="I73" s="6">
-        <f>I30/I28</f>
+        <f>(I28-I29)/I28</f>
         <v/>
       </c>
       <c r="J73" s="6">
-        <f>J30/J28</f>
+        <f>(J28-J29)/J28</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>研发费率</t>
+          <t>费率</t>
         </is>
       </c>
       <c r="D74" s="6">
-        <f>D31/D28</f>
+        <f>D30/D28</f>
         <v/>
       </c>
       <c r="E74" s="6">
-        <f>E31/E28</f>
+        <f>E30/E28</f>
         <v/>
       </c>
       <c r="F74" s="6">
-        <f>F31/F28</f>
+        <f>F30/F28</f>
         <v/>
       </c>
       <c r="G74" s="6">
-        <f>G31/G28</f>
+        <f>G30/G28</f>
         <v/>
       </c>
       <c r="H74" s="6">
-        <f>H31/H28</f>
+        <f>H30/H28</f>
         <v/>
       </c>
       <c r="I74" s="6">
-        <f>I31/I28</f>
+        <f>I30/I28</f>
         <v/>
       </c>
       <c r="J74" s="6">
-        <f>J31/J28</f>
+        <f>J30/J28</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>销售费率</t>
+          <t>研发费率</t>
         </is>
       </c>
       <c r="D75" s="6">
-        <f>D32/D28</f>
+        <f>D31/D28</f>
         <v/>
       </c>
       <c r="E75" s="6">
-        <f>E32/E28</f>
+        <f>E31/E28</f>
         <v/>
       </c>
       <c r="F75" s="6">
-        <f>F32/F28</f>
+        <f>F31/F28</f>
         <v/>
       </c>
       <c r="G75" s="6">
-        <f>G32/G28</f>
+        <f>G31/G28</f>
         <v/>
       </c>
       <c r="H75" s="6">
-        <f>H32/H28</f>
+        <f>H31/H28</f>
         <v/>
       </c>
       <c r="I75" s="6">
-        <f>I32/I28</f>
+        <f>I31/I28</f>
         <v/>
       </c>
       <c r="J75" s="6">
-        <f>J32/J28</f>
+        <f>J31/J28</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>管理费率</t>
+          <t>销售费率</t>
         </is>
       </c>
       <c r="D76" s="6">
-        <f>D33/D28</f>
+        <f>D32/D28</f>
         <v/>
       </c>
       <c r="E76" s="6">
-        <f>E33/E28</f>
+        <f>E32/E28</f>
         <v/>
       </c>
       <c r="F76" s="6">
-        <f>F33/F28</f>
+        <f>F32/F28</f>
         <v/>
       </c>
       <c r="G76" s="6">
-        <f>G33/G28</f>
+        <f>G32/G28</f>
         <v/>
       </c>
       <c r="H76" s="6">
-        <f>H33/H28</f>
+        <f>H32/H28</f>
         <v/>
       </c>
       <c r="I76" s="6">
-        <f>I33/I28</f>
+        <f>I32/I28</f>
         <v/>
       </c>
       <c r="J76" s="6">
-        <f>J33/J28</f>
+        <f>J32/J28</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
+          <t>管理费率</t>
+        </is>
+      </c>
+      <c r="D77" s="6">
+        <f>D33/D28</f>
+        <v/>
+      </c>
+      <c r="E77" s="6">
+        <f>E33/E28</f>
+        <v/>
+      </c>
+      <c r="F77" s="6">
+        <f>F33/F28</f>
+        <v/>
+      </c>
+      <c r="G77" s="6">
+        <f>G33/G28</f>
+        <v/>
+      </c>
+      <c r="H77" s="6">
+        <f>H33/H28</f>
+        <v/>
+      </c>
+      <c r="I77" s="6">
+        <f>I33/I28</f>
+        <v/>
+      </c>
+      <c r="J77" s="6">
+        <f>J33/J28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
           <t>净利率</t>
         </is>
       </c>
-      <c r="D77" s="6">
-        <f>D59/D28</f>
-        <v/>
-      </c>
-      <c r="E77" s="6">
-        <f>E59/E28</f>
-        <v/>
-      </c>
-      <c r="F77" s="6">
-        <f>F59/F28</f>
-        <v/>
-      </c>
-      <c r="G77" s="6">
-        <f>G59/G28</f>
-        <v/>
-      </c>
-      <c r="H77" s="6">
-        <f>H59/H28</f>
-        <v/>
-      </c>
-      <c r="I77" s="6">
-        <f>I59/I28</f>
-        <v/>
-      </c>
-      <c r="J77" s="6">
-        <f>J59/J28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>应收占比</t>
-        </is>
-      </c>
-      <c r="D79" s="6">
-        <f>D6/D28</f>
-        <v/>
-      </c>
-      <c r="E79" s="6">
-        <f>E6/E28</f>
-        <v/>
-      </c>
-      <c r="F79" s="6">
-        <f>F6/F28</f>
-        <v/>
-      </c>
-      <c r="G79" s="6">
-        <f>G6/G28</f>
-        <v/>
-      </c>
-      <c r="H79" s="6">
-        <f>H6/H28</f>
-        <v/>
-      </c>
-      <c r="I79" s="6">
-        <f>I6/I28</f>
-        <v/>
-      </c>
-      <c r="J79" s="6">
-        <f>J6/J28</f>
+      <c r="D78" s="6">
+        <f>D60/D28</f>
+        <v/>
+      </c>
+      <c r="E78" s="6">
+        <f>E60/E28</f>
+        <v/>
+      </c>
+      <c r="F78" s="6">
+        <f>F60/F28</f>
+        <v/>
+      </c>
+      <c r="G78" s="6">
+        <f>G60/G28</f>
+        <v/>
+      </c>
+      <c r="H78" s="6">
+        <f>H60/H28</f>
+        <v/>
+      </c>
+      <c r="I78" s="6">
+        <f>I60/I28</f>
+        <v/>
+      </c>
+      <c r="J78" s="6">
+        <f>J60/J28</f>
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>应收周转</t>
+          <t>应收占比</t>
         </is>
       </c>
       <c r="D80" s="6">
-        <f>D28/D6</f>
+        <f>D6/D28</f>
         <v/>
       </c>
       <c r="E80" s="6">
-        <f>E28/E6</f>
+        <f>E6/E28</f>
         <v/>
       </c>
       <c r="F80" s="6">
-        <f>F28/F6</f>
+        <f>F6/F28</f>
         <v/>
       </c>
       <c r="G80" s="6">
-        <f>G28/G6</f>
+        <f>G6/G28</f>
         <v/>
       </c>
       <c r="H80" s="6">
-        <f>H28/H6</f>
+        <f>H6/H28</f>
         <v/>
       </c>
       <c r="I80" s="6">
-        <f>I28/I6</f>
+        <f>I6/I28</f>
         <v/>
       </c>
       <c r="J80" s="6">
-        <f>J28/J6</f>
+        <f>J6/J28</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>存货周转</t>
+          <t>应收周转</t>
         </is>
       </c>
       <c r="D81" s="6">
-        <f>D29/D8</f>
+        <f>D28/D6</f>
         <v/>
       </c>
       <c r="E81" s="6">
-        <f>E29/E8</f>
+        <f>E28/E6</f>
         <v/>
       </c>
       <c r="F81" s="6">
-        <f>F29/F8</f>
+        <f>F28/F6</f>
         <v/>
       </c>
       <c r="G81" s="6">
-        <f>G29/G8</f>
+        <f>G28/G6</f>
         <v/>
       </c>
       <c r="H81" s="6">
-        <f>H29/H8</f>
+        <f>H28/H6</f>
         <v/>
       </c>
       <c r="I81" s="6">
-        <f>I29/I8</f>
+        <f>I28/I6</f>
         <v/>
       </c>
       <c r="J81" s="6">
-        <f>J29/J8</f>
+        <f>J28/J6</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>应付（预付）占比</t>
+          <t>存货周转</t>
         </is>
       </c>
       <c r="D82" s="6">
-        <f>(D12+D7)/D28</f>
+        <f>D29/D8</f>
         <v/>
       </c>
       <c r="E82" s="6">
-        <f>(E12+E7)/E28</f>
+        <f>E29/E8</f>
         <v/>
       </c>
       <c r="F82" s="6">
-        <f>(F12+F7)/F28</f>
+        <f>F29/F8</f>
         <v/>
       </c>
       <c r="G82" s="6">
-        <f>(G12+G7)/G28</f>
+        <f>G29/G8</f>
         <v/>
       </c>
       <c r="H82" s="6">
-        <f>(H12+H7)/H28</f>
+        <f>H29/H8</f>
         <v/>
       </c>
       <c r="I82" s="6">
-        <f>(I12+I7)/I28</f>
+        <f>I29/I8</f>
         <v/>
       </c>
       <c r="J82" s="6">
-        <f>(J12+J7)/J28</f>
+        <f>J29/J8</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>预收占比</t>
+          <t>应付（预付）占比</t>
         </is>
       </c>
       <c r="D83" s="6">
-        <f>D11/D28</f>
+        <f>(D12+D7)/D28</f>
         <v/>
       </c>
       <c r="E83" s="6">
-        <f>E11/E28</f>
+        <f>(E12+E7)/E28</f>
         <v/>
       </c>
       <c r="F83" s="6">
-        <f>F11/F28</f>
+        <f>(F12+F7)/F28</f>
         <v/>
       </c>
       <c r="G83" s="6">
-        <f>G11/G28</f>
+        <f>(G12+G7)/G28</f>
         <v/>
       </c>
       <c r="H83" s="6">
-        <f>H11/H28</f>
+        <f>(H12+H7)/H28</f>
         <v/>
       </c>
       <c r="I83" s="6">
-        <f>I11/I28</f>
+        <f>(I12+I7)/I28</f>
         <v/>
       </c>
       <c r="J83" s="6">
-        <f>J11/J28</f>
+        <f>(J12+J7)/J28</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>利息支出/业务利润</t>
+          <t>预收占比</t>
         </is>
       </c>
       <c r="D84" s="6">
-        <f>D38/D59</f>
+        <f>D11/D28</f>
         <v/>
       </c>
       <c r="E84" s="6">
-        <f>E38/E59</f>
+        <f>E11/E28</f>
         <v/>
       </c>
       <c r="F84" s="6">
-        <f>F38/F59</f>
+        <f>F11/F28</f>
         <v/>
       </c>
       <c r="G84" s="6">
-        <f>G38/G59</f>
+        <f>G11/G28</f>
         <v/>
       </c>
       <c r="H84" s="6">
-        <f>H38/H59</f>
+        <f>H11/H28</f>
         <v/>
       </c>
       <c r="I84" s="6">
-        <f>I38/I59</f>
+        <f>I11/I28</f>
         <v/>
       </c>
       <c r="J84" s="6">
-        <f>J38/J59</f>
+        <f>J11/J28</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
+          <t>利息支出/业务利润</t>
+        </is>
+      </c>
+      <c r="D85" s="6">
+        <f>D39/D60</f>
+        <v/>
+      </c>
+      <c r="E85" s="6">
+        <f>E39/E60</f>
+        <v/>
+      </c>
+      <c r="F85" s="6">
+        <f>F39/F60</f>
+        <v/>
+      </c>
+      <c r="G85" s="6">
+        <f>G39/G60</f>
+        <v/>
+      </c>
+      <c r="H85" s="6">
+        <f>H39/H60</f>
+        <v/>
+      </c>
+      <c r="I85" s="6">
+        <f>I39/I60</f>
+        <v/>
+      </c>
+      <c r="J85" s="6">
+        <f>J39/J60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
           <t>折旧摊销/长期资产</t>
         </is>
       </c>
-      <c r="D85" s="6">
+      <c r="D86" s="6">
         <f>D23/D9</f>
         <v/>
       </c>
-      <c r="E85" s="6">
+      <c r="E86" s="6">
         <f>E23/E9</f>
         <v/>
       </c>
-      <c r="F85" s="6">
+      <c r="F86" s="6">
         <f>F23/F9</f>
         <v/>
       </c>
-      <c r="G85" s="6">
+      <c r="G86" s="6">
         <f>G23/G9</f>
         <v/>
       </c>
-      <c r="H85" s="6">
+      <c r="H86" s="6">
         <f>H23/H9</f>
         <v/>
       </c>
-      <c r="I85" s="6">
+      <c r="I86" s="6">
         <f>I23/I9</f>
         <v/>
       </c>
-      <c r="J85" s="6">
+      <c r="J86" s="6">
         <f>J23/J9</f>
         <v/>
       </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>资产结构</t>
-        </is>
-      </c>
-      <c r="D87" s="4" t="n"/>
-      <c r="E87" s="4" t="n"/>
-      <c r="F87" s="4" t="n"/>
-      <c r="G87" s="4" t="n"/>
-      <c r="H87" s="4" t="n"/>
-      <c r="I87" s="4" t="n"/>
-      <c r="J87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>现金资产</t>
-        </is>
-      </c>
-      <c r="D88" s="6">
-        <f>D3/D2</f>
-        <v/>
-      </c>
-      <c r="E88" s="6">
-        <f>E3/E2</f>
-        <v/>
-      </c>
-      <c r="F88" s="6">
-        <f>F3/F2</f>
-        <v/>
-      </c>
-      <c r="G88" s="6">
-        <f>G3/G2</f>
-        <v/>
-      </c>
-      <c r="H88" s="6">
-        <f>H3/H2</f>
-        <v/>
-      </c>
-      <c r="I88" s="6">
-        <f>I3/I2</f>
-        <v/>
-      </c>
-      <c r="J88" s="6">
-        <f>J3/J2</f>
-        <v/>
-      </c>
+          <t>资产结构</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="n"/>
+      <c r="E88" s="4" t="n"/>
+      <c r="F88" s="4" t="n"/>
+      <c r="G88" s="4" t="n"/>
+      <c r="H88" s="4" t="n"/>
+      <c r="I88" s="4" t="n"/>
+      <c r="J88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>股权资产</t>
+          <t>现金资产</t>
         </is>
       </c>
       <c r="D89" s="6">
-        <f>D4/D2</f>
+        <f>D3/D2</f>
         <v/>
       </c>
       <c r="E89" s="6">
-        <f>E4/E2</f>
+        <f>E3/E2</f>
         <v/>
       </c>
       <c r="F89" s="6">
-        <f>F4/F2</f>
+        <f>F3/F2</f>
         <v/>
       </c>
       <c r="G89" s="6">
-        <f>G4/G2</f>
+        <f>G3/G2</f>
         <v/>
       </c>
       <c r="H89" s="6">
-        <f>H4/H2</f>
+        <f>H3/H2</f>
         <v/>
       </c>
       <c r="I89" s="6">
-        <f>I4/I2</f>
+        <f>I3/I2</f>
         <v/>
       </c>
       <c r="J89" s="6">
-        <f>J4/J2</f>
+        <f>J3/J2</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>经营资产</t>
+          <t>股权资产</t>
         </is>
       </c>
       <c r="D90" s="6">
-        <f>D5/D2</f>
+        <f>D4/D2</f>
         <v/>
       </c>
       <c r="E90" s="6">
-        <f>E5/E2</f>
+        <f>E4/E2</f>
         <v/>
       </c>
       <c r="F90" s="6">
-        <f>F5/F2</f>
+        <f>F4/F2</f>
         <v/>
       </c>
       <c r="G90" s="6">
-        <f>G5/G2</f>
+        <f>G4/G2</f>
         <v/>
       </c>
       <c r="H90" s="6">
-        <f>H5/H2</f>
+        <f>H4/H2</f>
         <v/>
       </c>
       <c r="I90" s="6">
-        <f>I5/I2</f>
+        <f>I4/I2</f>
         <v/>
       </c>
       <c r="J90" s="6">
-        <f>J5/J2</f>
+        <f>J4/J2</f>
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>长期资产</t>
+          <t>经营资产</t>
         </is>
       </c>
       <c r="D91" s="6">
-        <f>D9/D2</f>
+        <f>D5/D2</f>
         <v/>
       </c>
       <c r="E91" s="6">
-        <f>E9/E2</f>
+        <f>E5/E2</f>
         <v/>
       </c>
       <c r="F91" s="6">
-        <f>F9/F2</f>
+        <f>F5/F2</f>
         <v/>
       </c>
       <c r="G91" s="6">
-        <f>G9/G2</f>
+        <f>G5/G2</f>
         <v/>
       </c>
       <c r="H91" s="6">
-        <f>H9/H2</f>
+        <f>H5/H2</f>
         <v/>
       </c>
       <c r="I91" s="6">
-        <f>I9/I2</f>
+        <f>I5/I2</f>
         <v/>
       </c>
       <c r="J91" s="6">
-        <f>J9/J2</f>
+        <f>J5/J2</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>负债结构</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="n"/>
-      <c r="E92" s="4" t="n"/>
-      <c r="F92" s="4" t="n"/>
-      <c r="G92" s="4" t="n"/>
-      <c r="H92" s="4" t="n"/>
-      <c r="I92" s="4" t="n"/>
-      <c r="J92" s="4" t="n"/>
+          <t>长期资产</t>
+        </is>
+      </c>
+      <c r="D92" s="6">
+        <f>D9/D2</f>
+        <v/>
+      </c>
+      <c r="E92" s="6">
+        <f>E9/E2</f>
+        <v/>
+      </c>
+      <c r="F92" s="6">
+        <f>F9/F2</f>
+        <v/>
+      </c>
+      <c r="G92" s="6">
+        <f>G9/G2</f>
+        <v/>
+      </c>
+      <c r="H92" s="6">
+        <f>H9/H2</f>
+        <v/>
+      </c>
+      <c r="I92" s="6">
+        <f>I9/I2</f>
+        <v/>
+      </c>
+      <c r="J92" s="6">
+        <f>J9/J2</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>经营负债</t>
-        </is>
-      </c>
-      <c r="D93" s="6">
-        <f>(D11+D12)/D10</f>
-        <v/>
-      </c>
-      <c r="E93" s="6">
-        <f>(E11+E12)/E10</f>
-        <v/>
-      </c>
-      <c r="F93" s="6">
-        <f>(F11+F12)/F10</f>
-        <v/>
-      </c>
-      <c r="G93" s="6">
-        <f>(G11+G12)/G10</f>
-        <v/>
-      </c>
-      <c r="H93" s="6">
-        <f>(H11+H12)/H10</f>
-        <v/>
-      </c>
-      <c r="I93" s="6">
-        <f>(I11+I12)/I10</f>
-        <v/>
-      </c>
-      <c r="J93" s="6">
-        <f>(J11+J12)/J10</f>
-        <v/>
-      </c>
+          <t>负债结构</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="n"/>
+      <c r="E93" s="4" t="n"/>
+      <c r="F93" s="4" t="n"/>
+      <c r="G93" s="4" t="n"/>
+      <c r="H93" s="4" t="n"/>
+      <c r="I93" s="4" t="n"/>
+      <c r="J93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>有息负债</t>
+          <t>经营负债</t>
         </is>
       </c>
       <c r="D94" s="6">
-        <f>D13/D10</f>
+        <f>(D11+D12)/D10</f>
         <v/>
       </c>
       <c r="E94" s="6">
-        <f>E13/E10</f>
+        <f>(E11+E12)/E10</f>
         <v/>
       </c>
       <c r="F94" s="6">
-        <f>F13/F10</f>
+        <f>(F11+F12)/F10</f>
         <v/>
       </c>
       <c r="G94" s="6">
-        <f>G13/G10</f>
+        <f>(G11+G12)/G10</f>
         <v/>
       </c>
       <c r="H94" s="6">
-        <f>H13/H10</f>
+        <f>(H11+H12)/H10</f>
         <v/>
       </c>
       <c r="I94" s="6">
-        <f>I13/I10</f>
+        <f>(I11+I12)/I10</f>
         <v/>
       </c>
       <c r="J94" s="6">
-        <f>J13/J10</f>
+        <f>(J11+J12)/J10</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>权益结构</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="n"/>
-      <c r="E95" s="4" t="n"/>
-      <c r="F95" s="4" t="n"/>
-      <c r="G95" s="4" t="n"/>
-      <c r="H95" s="4" t="n"/>
-      <c r="I95" s="4" t="n"/>
-      <c r="J95" s="4" t="n"/>
+          <t>有息负债</t>
+        </is>
+      </c>
+      <c r="D95" s="6">
+        <f>D13/D10</f>
+        <v/>
+      </c>
+      <c r="E95" s="6">
+        <f>E13/E10</f>
+        <v/>
+      </c>
+      <c r="F95" s="6">
+        <f>F13/F10</f>
+        <v/>
+      </c>
+      <c r="G95" s="6">
+        <f>G13/G10</f>
+        <v/>
+      </c>
+      <c r="H95" s="6">
+        <f>H13/H10</f>
+        <v/>
+      </c>
+      <c r="I95" s="6">
+        <f>I13/I10</f>
+        <v/>
+      </c>
+      <c r="J95" s="6">
+        <f>J13/J10</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>资本投入</t>
-        </is>
-      </c>
-      <c r="D96" s="6">
-        <f>D15/D14</f>
-        <v/>
-      </c>
-      <c r="E96" s="6">
-        <f>E15/E14</f>
-        <v/>
-      </c>
-      <c r="F96" s="6">
-        <f>F15/F14</f>
-        <v/>
-      </c>
-      <c r="G96" s="6">
-        <f>G15/G14</f>
-        <v/>
-      </c>
-      <c r="H96" s="6">
-        <f>H15/H14</f>
-        <v/>
-      </c>
-      <c r="I96" s="6">
-        <f>I15/I14</f>
-        <v/>
-      </c>
-      <c r="J96" s="6">
-        <f>J15/J14</f>
-        <v/>
-      </c>
+          <t>权益结构</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="n"/>
+      <c r="E96" s="4" t="n"/>
+      <c r="F96" s="4" t="n"/>
+      <c r="G96" s="4" t="n"/>
+      <c r="H96" s="4" t="n"/>
+      <c r="I96" s="4" t="n"/>
+      <c r="J96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
+          <t>资本投入</t>
+        </is>
+      </c>
+      <c r="D97" s="6">
+        <f>D15/D14</f>
+        <v/>
+      </c>
+      <c r="E97" s="6">
+        <f>E15/E14</f>
+        <v/>
+      </c>
+      <c r="F97" s="6">
+        <f>F15/F14</f>
+        <v/>
+      </c>
+      <c r="G97" s="6">
+        <f>G15/G14</f>
+        <v/>
+      </c>
+      <c r="H97" s="6">
+        <f>H15/H14</f>
+        <v/>
+      </c>
+      <c r="I97" s="6">
+        <f>I15/I14</f>
+        <v/>
+      </c>
+      <c r="J97" s="6">
+        <f>J15/J14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
           <t>利润留存</t>
         </is>
       </c>
-      <c r="D97" s="6">
+      <c r="D98" s="6">
         <f>D16/D14</f>
         <v/>
       </c>
-      <c r="E97" s="6">
+      <c r="E98" s="6">
         <f>E16/E14</f>
         <v/>
       </c>
-      <c r="F97" s="6">
+      <c r="F98" s="6">
         <f>F16/F14</f>
         <v/>
       </c>
-      <c r="G97" s="6">
+      <c r="G98" s="6">
         <f>G16/G14</f>
         <v/>
       </c>
-      <c r="H97" s="6">
+      <c r="H98" s="6">
         <f>H16/H14</f>
         <v/>
       </c>
-      <c r="I97" s="6">
+      <c r="I98" s="6">
         <f>I16/I14</f>
         <v/>
       </c>
-      <c r="J97" s="6">
+      <c r="J98" s="6">
         <f>J16/J14</f>
         <v/>
       </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>营收YoY</t>
-        </is>
-      </c>
-      <c r="D99" s="6">
-        <f>(D28-E28)/E28</f>
-        <v/>
-      </c>
-      <c r="E99" s="6">
-        <f>(E28-F28)/F28</f>
-        <v/>
-      </c>
-      <c r="F99" s="6">
-        <f>(F28-G28)/G28</f>
-        <v/>
-      </c>
-      <c r="G99" s="6">
-        <f>(G28-H28)/H28</f>
-        <v/>
-      </c>
-      <c r="H99" s="6">
-        <f>(H28-I28)/I28</f>
-        <v/>
-      </c>
-      <c r="I99" s="6">
-        <f>(I28-J28)/J28</f>
-        <v/>
-      </c>
-      <c r="J99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
+          <t>营收YoY</t>
+        </is>
+      </c>
+      <c r="D100" s="6">
+        <f>(D28-E28)/E28</f>
+        <v/>
+      </c>
+      <c r="E100" s="6">
+        <f>(E28-F28)/F28</f>
+        <v/>
+      </c>
+      <c r="F100" s="6">
+        <f>(F28-G28)/G28</f>
+        <v/>
+      </c>
+      <c r="G100" s="6">
+        <f>(G28-H28)/H28</f>
+        <v/>
+      </c>
+      <c r="H100" s="6">
+        <f>(H28-I28)/I28</f>
+        <v/>
+      </c>
+      <c r="I100" s="6">
+        <f>(I28-J28)/J28</f>
+        <v/>
+      </c>
+      <c r="J100" s="7" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
           <t>业务净利润YoY</t>
         </is>
       </c>
-      <c r="D100" s="6">
-        <f>(D59-E59)/E59</f>
-        <v/>
-      </c>
-      <c r="E100" s="6">
-        <f>(E59-F59)/F59</f>
-        <v/>
-      </c>
-      <c r="F100" s="6">
-        <f>(F59-G59)/G59</f>
-        <v/>
-      </c>
-      <c r="G100" s="6">
-        <f>(G59-H59)/H59</f>
-        <v/>
-      </c>
-      <c r="H100" s="6">
-        <f>(H59-I59)/I59</f>
-        <v/>
-      </c>
-      <c r="I100" s="6">
-        <f>(I59-J59)/J59</f>
-        <v/>
-      </c>
-      <c r="J100" s="7" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
+      <c r="D101" s="6">
+        <f>(D60-E60)/E60</f>
+        <v/>
+      </c>
+      <c r="E101" s="6">
+        <f>(E60-F60)/F60</f>
+        <v/>
+      </c>
+      <c r="F101" s="6">
+        <f>(F60-G60)/G60</f>
+        <v/>
+      </c>
+      <c r="G101" s="6">
+        <f>(G60-H60)/H60</f>
+        <v/>
+      </c>
+      <c r="H101" s="6">
+        <f>(H60-I60)/I60</f>
+        <v/>
+      </c>
+      <c r="I101" s="6">
+        <f>(I60-J60)/J60</f>
+        <v/>
+      </c>
+      <c r="J101" s="7" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>资产YoY</t>
         </is>
       </c>
-      <c r="D102" s="6">
+      <c r="D103" s="6">
         <f>(D2-E2)/E2</f>
         <v/>
       </c>
-      <c r="E102" s="6">
+      <c r="E103" s="6">
         <f>(E2-F2)/F2</f>
         <v/>
       </c>
-      <c r="F102" s="6">
+      <c r="F103" s="6">
         <f>(F2-G2)/G2</f>
         <v/>
       </c>
-      <c r="G102" s="6">
+      <c r="G103" s="6">
         <f>(G2-H2)/H2</f>
         <v/>
       </c>
-      <c r="H102" s="6">
+      <c r="H103" s="6">
         <f>(H2-I2)/I2</f>
         <v/>
       </c>
-      <c r="I102" s="6">
+      <c r="I103" s="6">
         <f>(I2-J2)/J2</f>
-        <v/>
-      </c>
-      <c r="J102" s="7" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>现金</t>
-        </is>
-      </c>
-      <c r="D103" s="6">
-        <f>(D3-E3)/E3</f>
-        <v/>
-      </c>
-      <c r="E103" s="6">
-        <f>(E3-F3)/F3</f>
-        <v/>
-      </c>
-      <c r="F103" s="6">
-        <f>(F3-G3)/G3</f>
-        <v/>
-      </c>
-      <c r="G103" s="6">
-        <f>(G3-H3)/H3</f>
-        <v/>
-      </c>
-      <c r="H103" s="6">
-        <f>(H3-I3)/I3</f>
-        <v/>
-      </c>
-      <c r="I103" s="6">
-        <f>(I3-J3)/J3</f>
         <v/>
       </c>
       <c r="J103" s="7" t="n"/>
@@ -3299,31 +3295,31 @@
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>投资</t>
+          <t>现金</t>
         </is>
       </c>
       <c r="D104" s="6">
-        <f>(D4-E4)/E4</f>
+        <f>(D3-E3)/E3</f>
         <v/>
       </c>
       <c r="E104" s="6">
-        <f>(E4-F4)/F4</f>
+        <f>(E3-F3)/F3</f>
         <v/>
       </c>
       <c r="F104" s="6">
-        <f>(F4-G4)/G4</f>
+        <f>(F3-G3)/G3</f>
         <v/>
       </c>
       <c r="G104" s="6">
-        <f>(G4-H4)/H4</f>
+        <f>(G3-H3)/H3</f>
         <v/>
       </c>
       <c r="H104" s="6">
-        <f>(H4-I4)/I4</f>
+        <f>(H3-I3)/I3</f>
         <v/>
       </c>
       <c r="I104" s="6">
-        <f>(I4-J4)/J4</f>
+        <f>(I3-J3)/J3</f>
         <v/>
       </c>
       <c r="J104" s="7" t="n"/>
@@ -3331,31 +3327,31 @@
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>运营资产</t>
+          <t>投资</t>
         </is>
       </c>
       <c r="D105" s="6">
-        <f>(D5-E5)/E5</f>
+        <f>(D4-E4)/E4</f>
         <v/>
       </c>
       <c r="E105" s="6">
-        <f>(E5-F5)/F5</f>
+        <f>(E4-F4)/F4</f>
         <v/>
       </c>
       <c r="F105" s="6">
-        <f>(F5-G5)/G5</f>
+        <f>(F4-G4)/G4</f>
         <v/>
       </c>
       <c r="G105" s="6">
-        <f>(G5-H5)/H5</f>
+        <f>(G4-H4)/H4</f>
         <v/>
       </c>
       <c r="H105" s="6">
-        <f>(H5-I5)/I5</f>
+        <f>(H4-I4)/I4</f>
         <v/>
       </c>
       <c r="I105" s="6">
-        <f>(I5-J5)/J5</f>
+        <f>(I4-J4)/J4</f>
         <v/>
       </c>
       <c r="J105" s="7" t="n"/>
@@ -3363,95 +3359,95 @@
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
+          <t>运营资产</t>
+        </is>
+      </c>
+      <c r="D106" s="6">
+        <f>(D5-E5)/E5</f>
+        <v/>
+      </c>
+      <c r="E106" s="6">
+        <f>(E5-F5)/F5</f>
+        <v/>
+      </c>
+      <c r="F106" s="6">
+        <f>(F5-G5)/G5</f>
+        <v/>
+      </c>
+      <c r="G106" s="6">
+        <f>(G5-H5)/H5</f>
+        <v/>
+      </c>
+      <c r="H106" s="6">
+        <f>(H5-I5)/I5</f>
+        <v/>
+      </c>
+      <c r="I106" s="6">
+        <f>(I5-J5)/J5</f>
+        <v/>
+      </c>
+      <c r="J106" s="7" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
           <t>长期资产</t>
         </is>
       </c>
-      <c r="D106" s="6">
+      <c r="D107" s="6">
         <f>(D9-E9)/E9</f>
         <v/>
       </c>
-      <c r="E106" s="6">
+      <c r="E107" s="6">
         <f>(E9-F9)/F9</f>
         <v/>
       </c>
-      <c r="F106" s="6">
+      <c r="F107" s="6">
         <f>(F9-G9)/G9</f>
         <v/>
       </c>
-      <c r="G106" s="6">
+      <c r="G107" s="6">
         <f>(G9-H9)/H9</f>
         <v/>
       </c>
-      <c r="H106" s="6">
+      <c r="H107" s="6">
         <f>(H9-I9)/I9</f>
         <v/>
       </c>
-      <c r="I106" s="6">
+      <c r="I107" s="6">
         <f>(I9-J9)/J9</f>
         <v/>
       </c>
-      <c r="J106" s="7" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
+      <c r="J107" s="7" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>权益YoY</t>
         </is>
       </c>
-      <c r="D107" s="6">
+      <c r="D108" s="6">
         <f>(D14-E14)/E14</f>
         <v/>
       </c>
-      <c r="E107" s="6">
+      <c r="E108" s="6">
         <f>(E14-F14)/F14</f>
         <v/>
       </c>
-      <c r="F107" s="6">
+      <c r="F108" s="6">
         <f>(F14-G14)/G14</f>
         <v/>
       </c>
-      <c r="G107" s="6">
+      <c r="G108" s="6">
         <f>(G14-H14)/H14</f>
         <v/>
       </c>
-      <c r="H107" s="6">
+      <c r="H108" s="6">
         <f>(H14-I14)/I14</f>
         <v/>
       </c>
-      <c r="I107" s="6">
+      <c r="I108" s="6">
         <f>(I14-J14)/J14</f>
-        <v/>
-      </c>
-      <c r="J107" s="7" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>资本投入</t>
-        </is>
-      </c>
-      <c r="D108" s="6">
-        <f>(D15-E15)/E15</f>
-        <v/>
-      </c>
-      <c r="E108" s="6">
-        <f>(E15-F15)/F15</f>
-        <v/>
-      </c>
-      <c r="F108" s="6">
-        <f>(F15-G15)/G15</f>
-        <v/>
-      </c>
-      <c r="G108" s="6">
-        <f>(G15-H15)/H15</f>
-        <v/>
-      </c>
-      <c r="H108" s="6">
-        <f>(H15-I15)/I15</f>
-        <v/>
-      </c>
-      <c r="I108" s="6">
-        <f>(I15-J15)/J15</f>
         <v/>
       </c>
       <c r="J108" s="7" t="n"/>
@@ -3459,95 +3455,95 @@
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
+          <t>资本投入</t>
+        </is>
+      </c>
+      <c r="D109" s="6">
+        <f>(D15-E15)/E15</f>
+        <v/>
+      </c>
+      <c r="E109" s="6">
+        <f>(E15-F15)/F15</f>
+        <v/>
+      </c>
+      <c r="F109" s="6">
+        <f>(F15-G15)/G15</f>
+        <v/>
+      </c>
+      <c r="G109" s="6">
+        <f>(G15-H15)/H15</f>
+        <v/>
+      </c>
+      <c r="H109" s="6">
+        <f>(H15-I15)/I15</f>
+        <v/>
+      </c>
+      <c r="I109" s="6">
+        <f>(I15-J15)/J15</f>
+        <v/>
+      </c>
+      <c r="J109" s="7" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
           <t>未分配利润</t>
         </is>
       </c>
-      <c r="D109" s="6">
+      <c r="D110" s="6">
         <f>(D16-E16)/E16</f>
         <v/>
       </c>
-      <c r="E109" s="6">
+      <c r="E110" s="6">
         <f>(E16-F16)/F16</f>
         <v/>
       </c>
-      <c r="F109" s="6">
+      <c r="F110" s="6">
         <f>(F16-G16)/G16</f>
         <v/>
       </c>
-      <c r="G109" s="6">
+      <c r="G110" s="6">
         <f>(G16-H16)/H16</f>
         <v/>
       </c>
-      <c r="H109" s="6">
+      <c r="H110" s="6">
         <f>(H16-I16)/I16</f>
         <v/>
       </c>
-      <c r="I109" s="6">
+      <c r="I110" s="6">
         <f>(I16-J16)/J16</f>
         <v/>
       </c>
-      <c r="J109" s="7" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
+      <c r="J110" s="7" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>负债YoY</t>
         </is>
       </c>
-      <c r="D110" s="6">
+      <c r="D111" s="6">
         <f>(D10-E10)/E10</f>
         <v/>
       </c>
-      <c r="E110" s="6">
+      <c r="E111" s="6">
         <f>(E10-F10)/F10</f>
         <v/>
       </c>
-      <c r="F110" s="6">
+      <c r="F111" s="6">
         <f>(F10-G10)/G10</f>
         <v/>
       </c>
-      <c r="G110" s="6">
+      <c r="G111" s="6">
         <f>(G10-H10)/H10</f>
         <v/>
       </c>
-      <c r="H110" s="6">
+      <c r="H111" s="6">
         <f>(H10-I10)/I10</f>
         <v/>
       </c>
-      <c r="I110" s="6">
+      <c r="I111" s="6">
         <f>(I10-J10)/J10</f>
-        <v/>
-      </c>
-      <c r="J110" s="7" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>预收</t>
-        </is>
-      </c>
-      <c r="D111" s="6">
-        <f>(D11-E11)/E11</f>
-        <v/>
-      </c>
-      <c r="E111" s="6">
-        <f>(E11-F11)/F11</f>
-        <v/>
-      </c>
-      <c r="F111" s="6">
-        <f>(F11-G11)/G11</f>
-        <v/>
-      </c>
-      <c r="G111" s="6">
-        <f>(G11-H11)/H11</f>
-        <v/>
-      </c>
-      <c r="H111" s="6">
-        <f>(H11-I11)/I11</f>
-        <v/>
-      </c>
-      <c r="I111" s="6">
-        <f>(I11-J11)/J11</f>
         <v/>
       </c>
       <c r="J111" s="7" t="n"/>
@@ -3555,31 +3551,31 @@
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>应付</t>
+          <t>预收</t>
         </is>
       </c>
       <c r="D112" s="6">
-        <f>(D12-E12)/E12</f>
+        <f>(D11-E11)/E11</f>
         <v/>
       </c>
       <c r="E112" s="6">
-        <f>(E12-F12)/F12</f>
+        <f>(E11-F11)/F11</f>
         <v/>
       </c>
       <c r="F112" s="6">
-        <f>(F12-G12)/G12</f>
+        <f>(F11-G11)/G11</f>
         <v/>
       </c>
       <c r="G112" s="6">
-        <f>(G12-H12)/H12</f>
+        <f>(G11-H11)/H11</f>
         <v/>
       </c>
       <c r="H112" s="6">
-        <f>(H12-I12)/I12</f>
+        <f>(H11-I11)/I11</f>
         <v/>
       </c>
       <c r="I112" s="6">
-        <f>(I12-J12)/J12</f>
+        <f>(I11-J11)/J11</f>
         <v/>
       </c>
       <c r="J112" s="7" t="n"/>
@@ -3587,188 +3583,206 @@
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
+          <t>应付</t>
+        </is>
+      </c>
+      <c r="D113" s="6">
+        <f>(D12-E12)/E12</f>
+        <v/>
+      </c>
+      <c r="E113" s="6">
+        <f>(E12-F12)/F12</f>
+        <v/>
+      </c>
+      <c r="F113" s="6">
+        <f>(F12-G12)/G12</f>
+        <v/>
+      </c>
+      <c r="G113" s="6">
+        <f>(G12-H12)/H12</f>
+        <v/>
+      </c>
+      <c r="H113" s="6">
+        <f>(H12-I12)/I12</f>
+        <v/>
+      </c>
+      <c r="I113" s="6">
+        <f>(I12-J12)/J12</f>
+        <v/>
+      </c>
+      <c r="J113" s="7" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
           <t>有息债务</t>
         </is>
       </c>
-      <c r="D113" s="6">
+      <c r="D114" s="6">
         <f>(D13-E13)/E13</f>
         <v/>
       </c>
-      <c r="E113" s="6">
+      <c r="E114" s="6">
         <f>(E13-F13)/F13</f>
         <v/>
       </c>
-      <c r="F113" s="6">
+      <c r="F114" s="6">
         <f>(F13-G13)/G13</f>
         <v/>
       </c>
-      <c r="G113" s="6">
+      <c r="G114" s="6">
         <f>(G13-H13)/H13</f>
         <v/>
       </c>
-      <c r="H113" s="6">
+      <c r="H114" s="6">
         <f>(H13-I13)/I13</f>
         <v/>
       </c>
-      <c r="I113" s="6">
+      <c r="I114" s="6">
         <f>(I13-J13)/J13</f>
         <v/>
       </c>
-      <c r="J113" s="7" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
+      <c r="J114" s="7" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="D115" s="6">
-        <f>D59/D14</f>
-        <v/>
-      </c>
-      <c r="E115" s="6">
-        <f>E59/E14</f>
-        <v/>
-      </c>
-      <c r="F115" s="6">
-        <f>F59/F14</f>
-        <v/>
-      </c>
-      <c r="G115" s="6">
-        <f>G59/G14</f>
-        <v/>
-      </c>
-      <c r="H115" s="6">
-        <f>H59/H14</f>
-        <v/>
-      </c>
-      <c r="I115" s="6">
-        <f>I59/I14</f>
-        <v/>
-      </c>
-      <c r="J115" s="6">
-        <f>J59/J14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="inlineStr">
-        <is>
-          <t>Net Proit</t>
-        </is>
-      </c>
       <c r="D116" s="6">
-        <f>D59/D28</f>
+        <f>D60/D14</f>
         <v/>
       </c>
       <c r="E116" s="6">
-        <f>E59/E28</f>
+        <f>E60/E14</f>
         <v/>
       </c>
       <c r="F116" s="6">
-        <f>F59/F28</f>
+        <f>F60/F14</f>
         <v/>
       </c>
       <c r="G116" s="6">
-        <f>G59/G28</f>
+        <f>G60/G14</f>
         <v/>
       </c>
       <c r="H116" s="6">
-        <f>H59/H28</f>
+        <f>H60/H14</f>
         <v/>
       </c>
       <c r="I116" s="6">
-        <f>I59/I28</f>
+        <f>I60/I14</f>
         <v/>
       </c>
       <c r="J116" s="6">
-        <f>J59/J28</f>
+        <f>J60/J14</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>主营收入/资产</t>
+          <t>Net Proit</t>
         </is>
       </c>
       <c r="D117" s="6">
-        <f>D28/D2</f>
+        <f>D60/D28</f>
         <v/>
       </c>
       <c r="E117" s="6">
-        <f>E28/E2</f>
+        <f>E60/E28</f>
         <v/>
       </c>
       <c r="F117" s="6">
-        <f>F28/F2</f>
+        <f>F60/F28</f>
         <v/>
       </c>
       <c r="G117" s="6">
-        <f>G28/G2</f>
+        <f>G60/G28</f>
         <v/>
       </c>
       <c r="H117" s="6">
-        <f>H28/H2</f>
+        <f>H60/H28</f>
         <v/>
       </c>
       <c r="I117" s="6">
-        <f>I28/I2</f>
+        <f>I60/I28</f>
         <v/>
       </c>
       <c r="J117" s="6">
-        <f>J28/J2</f>
+        <f>J60/J28</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
+          <t>主营收入/资产</t>
+        </is>
+      </c>
+      <c r="D118" s="6">
+        <f>D28/D2</f>
+        <v/>
+      </c>
+      <c r="E118" s="6">
+        <f>E28/E2</f>
+        <v/>
+      </c>
+      <c r="F118" s="6">
+        <f>F28/F2</f>
+        <v/>
+      </c>
+      <c r="G118" s="6">
+        <f>G28/G2</f>
+        <v/>
+      </c>
+      <c r="H118" s="6">
+        <f>H28/H2</f>
+        <v/>
+      </c>
+      <c r="I118" s="6">
+        <f>I28/I2</f>
+        <v/>
+      </c>
+      <c r="J118" s="6">
+        <f>J28/J2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
           <t>资产/资本</t>
         </is>
       </c>
-      <c r="D118" s="6">
+      <c r="D119" s="6">
         <f>D2/D14</f>
         <v/>
       </c>
-      <c r="E118" s="6">
+      <c r="E119" s="6">
         <f>E2/E14</f>
         <v/>
       </c>
-      <c r="F118" s="6">
+      <c r="F119" s="6">
         <f>F2/F14</f>
         <v/>
       </c>
-      <c r="G118" s="6">
+      <c r="G119" s="6">
         <f>G2/G14</f>
         <v/>
       </c>
-      <c r="H118" s="6">
+      <c r="H119" s="6">
         <f>H2/H14</f>
         <v/>
       </c>
-      <c r="I118" s="6">
+      <c r="I119" s="6">
         <f>I2/I14</f>
         <v/>
       </c>
-      <c r="J118" s="6">
+      <c r="J119" s="6">
         <f>J2/J14</f>
         <v/>
       </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>股息</t>
-        </is>
-      </c>
-      <c r="D120" s="4" t="n"/>
-      <c r="E120" s="4" t="n"/>
-      <c r="F120" s="4" t="n"/>
-      <c r="G120" s="4" t="n"/>
-      <c r="H120" s="4" t="n"/>
-      <c r="I120" s="4" t="n"/>
-      <c r="J120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -3777,31 +3791,31 @@
         </is>
       </c>
       <c r="D121" s="6">
-        <f>D59/D26</f>
+        <f>D60/D26</f>
         <v/>
       </c>
       <c r="E121" s="6">
-        <f>E59/E26</f>
+        <f>E60/E26</f>
         <v/>
       </c>
       <c r="F121" s="6">
-        <f>F59/F26</f>
+        <f>F60/F26</f>
         <v/>
       </c>
       <c r="G121" s="6">
-        <f>G59/G26</f>
+        <f>G60/G26</f>
         <v/>
       </c>
       <c r="H121" s="6">
-        <f>H59/H26</f>
+        <f>H60/H26</f>
         <v/>
       </c>
       <c r="I121" s="6">
-        <f>I59/I26</f>
+        <f>I60/I26</f>
         <v/>
       </c>
       <c r="J121" s="6">
-        <f>J59/J26</f>
+        <f>J60/J26</f>
         <v/>
       </c>
     </row>
@@ -3812,31 +3826,31 @@
         </is>
       </c>
       <c r="D122" s="6">
-        <f>D69/D26</f>
+        <f>D70/D26</f>
         <v/>
       </c>
       <c r="E122" s="6">
-        <f>E69/E26</f>
+        <f>E70/E26</f>
         <v/>
       </c>
       <c r="F122" s="6">
-        <f>F69/F26</f>
+        <f>F70/F26</f>
         <v/>
       </c>
       <c r="G122" s="6">
-        <f>G69/G26</f>
+        <f>G70/G26</f>
         <v/>
       </c>
       <c r="H122" s="6">
-        <f>H69/H26</f>
+        <f>H70/H26</f>
         <v/>
       </c>
       <c r="I122" s="6">
-        <f>I69/I26</f>
+        <f>I70/I26</f>
         <v/>
       </c>
       <c r="J122" s="6">
-        <f>J69/J26</f>
+        <f>J70/J26</f>
         <v/>
       </c>
     </row>
@@ -3875,31 +3889,31 @@
         </is>
       </c>
       <c r="D126" s="6">
-        <f>D124/(D59/D26)</f>
+        <f>D124/(D60/D26)</f>
         <v/>
       </c>
       <c r="E126" s="6">
-        <f>E124/(E59/E26)</f>
+        <f>E124/(E60/E26)</f>
         <v/>
       </c>
       <c r="F126" s="6">
-        <f>F124/(F59/F26)</f>
+        <f>F124/(F60/F26)</f>
         <v/>
       </c>
       <c r="G126" s="6">
-        <f>G124/(G59/G26)</f>
+        <f>G124/(G60/G26)</f>
         <v/>
       </c>
       <c r="H126" s="6">
-        <f>H124/(H59/H26)</f>
+        <f>H124/(H60/H26)</f>
         <v/>
       </c>
       <c r="I126" s="6">
-        <f>I124/(I59/I26)</f>
+        <f>I124/(I60/I26)</f>
         <v/>
       </c>
       <c r="J126" s="6">
-        <f>J124/(J59/J26)</f>
+        <f>J124/(J60/J26)</f>
         <v/>
       </c>
     </row>
@@ -3910,31 +3924,31 @@
         </is>
       </c>
       <c r="D127" s="6">
-        <f>D125/(D59/D26)</f>
+        <f>D125/(D60/D26)</f>
         <v/>
       </c>
       <c r="E127" s="6">
-        <f>E125/(E59/E26)</f>
+        <f>E125/(E60/E26)</f>
         <v/>
       </c>
       <c r="F127" s="6">
-        <f>F125/(F59/F26)</f>
+        <f>F125/(F60/F26)</f>
         <v/>
       </c>
       <c r="G127" s="6">
-        <f>G125/(G59/G26)</f>
+        <f>G125/(G60/G26)</f>
         <v/>
       </c>
       <c r="H127" s="6">
-        <f>H125/(H59/H26)</f>
+        <f>H125/(H60/H26)</f>
         <v/>
       </c>
       <c r="I127" s="6">
-        <f>I125/(I59/I26)</f>
+        <f>I125/(I60/I26)</f>
         <v/>
       </c>
       <c r="J127" s="6">
-        <f>J125/(J59/J26)</f>
+        <f>J125/(J60/J26)</f>
         <v/>
       </c>
     </row>
@@ -3945,31 +3959,31 @@
         </is>
       </c>
       <c r="D128" s="6">
-        <f>(D17/D26)/D124</f>
+        <f>D17/(D124*D26)</f>
         <v/>
       </c>
       <c r="E128" s="6">
-        <f>(E17/E26)/E124</f>
+        <f>E17/(E124*E26)</f>
         <v/>
       </c>
       <c r="F128" s="6">
-        <f>(F17/F26)/F124</f>
+        <f>F17/(F124*F26)</f>
         <v/>
       </c>
       <c r="G128" s="6">
-        <f>(G17/G26)/G124</f>
+        <f>G17/(G124*G26)</f>
         <v/>
       </c>
       <c r="H128" s="6">
-        <f>(H17/H26)/H124</f>
+        <f>H17/(H124*H26)</f>
         <v/>
       </c>
       <c r="I128" s="6">
-        <f>(I17/I26)/I124</f>
+        <f>I17/(I124*I26)</f>
         <v/>
       </c>
       <c r="J128" s="6">
-        <f>(J17/J26)/J124</f>
+        <f>J17/(J124*J26)</f>
         <v/>
       </c>
     </row>
@@ -3980,31 +3994,31 @@
         </is>
       </c>
       <c r="D129" s="6">
-        <f>(D17/D26)/D125</f>
+        <f>D17/(D125*D26)</f>
         <v/>
       </c>
       <c r="E129" s="6">
-        <f>(E17/E26)/E125</f>
+        <f>E17/(E125*E26)</f>
         <v/>
       </c>
       <c r="F129" s="6">
-        <f>(F17/F26)/F125</f>
+        <f>F17/(F125*F26)</f>
         <v/>
       </c>
       <c r="G129" s="6">
-        <f>(G17/G26)/G125</f>
+        <f>G17/(G125*G26)</f>
         <v/>
       </c>
       <c r="H129" s="6">
-        <f>(H17/H26)/H125</f>
+        <f>H17/(H125*H26)</f>
         <v/>
       </c>
       <c r="I129" s="6">
-        <f>(I17/I26)/I125</f>
+        <f>I17/(I125*I26)</f>
         <v/>
       </c>
       <c r="J129" s="6">
-        <f>(J17/J26)/J125</f>
+        <f>J17/(J125*J26)</f>
         <v/>
       </c>
     </row>
